--- a/AutomateSendingOutTaxReturnsV3.xlsx
+++ b/AutomateSendingOutTaxReturnsV3.xlsx
@@ -22,7 +22,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -30,6 +30,30 @@
     </fill>
     <fill>
       <patternFill patternType="gray125">
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FF00"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FF00"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -53,10 +77,14 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -388,7 +416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:Q4"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="str">
@@ -436,6 +464,12 @@
       <c r="O1" s="2" t="str">
         <v>Pipeline</v>
       </c>
+      <c r="P1" s="2" t="str">
+        <v>Seal</v>
+      </c>
+      <c r="Q1" s="2" t="str">
+        <v>YearToSeal</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2">
@@ -448,7 +482,7 @@
         <v>Single, Dummy</v>
       </c>
       <c r="D2" s="2" t="str">
-        <v>Send CRM Code</v>
+        <v>none</v>
       </c>
       <c r="E2" s="2" t="str">
         <v>none</v>
@@ -457,19 +491,19 @@
         <v>Nice!</v>
       </c>
       <c r="G2" s="2" t="str">
-        <v>X</v>
+        <v>none</v>
       </c>
       <c r="H2" s="2" t="str">
-        <v>X</v>
+        <v>none</v>
       </c>
       <c r="I2" s="2" t="str">
-        <v>X</v>
+        <v>none</v>
       </c>
       <c r="J2" s="2" t="str">
         <v>MA-Single</v>
       </c>
       <c r="K2" s="2" t="str">
-        <v>X</v>
+        <v>none</v>
       </c>
       <c r="L2" s="2">
         <v>750</v>
@@ -478,10 +512,16 @@
         <v>Personal Tax Services - JJ</v>
       </c>
       <c r="N2" s="2" t="str">
-        <v>X</v>
+        <v>none</v>
       </c>
       <c r="O2" s="2" t="str">
         <v>2022 1040 Return - JJ</v>
+      </c>
+      <c r="P2" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>2023</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +535,7 @@
         <v>DummyDiffLastName, Married &amp; WeirdDiff-LastName, Spouse</v>
       </c>
       <c r="D3" s="2" t="str">
-        <v>Send CRM Code</v>
+        <v>none</v>
       </c>
       <c r="E3" s="2" t="str">
         <v>none</v>
@@ -504,19 +544,19 @@
         <v>Great!</v>
       </c>
       <c r="G3" s="2" t="str">
-        <v>X</v>
+        <v>none</v>
       </c>
       <c r="H3" s="2" t="str">
-        <v>X</v>
+        <v>none</v>
       </c>
       <c r="I3" s="2" t="str">
-        <v>X</v>
+        <v>none</v>
       </c>
       <c r="J3" s="2" t="str">
         <v>MA-Single</v>
       </c>
       <c r="K3" s="2" t="str">
-        <v>X</v>
+        <v>none</v>
       </c>
       <c r="L3" s="2">
         <v>1000</v>
@@ -525,10 +565,16 @@
         <v>Personal Tax Services - JJ</v>
       </c>
       <c r="N3" s="2" t="str">
-        <v>X</v>
+        <v>none</v>
       </c>
       <c r="O3" s="2" t="str">
         <v>2022 1040 Return - JJ</v>
+      </c>
+      <c r="P3" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>2023</v>
       </c>
     </row>
     <row r="4">
@@ -542,7 +588,7 @@
         <v>Single, Dummy</v>
       </c>
       <c r="D4" s="2" t="str">
-        <v>Send CRM Code</v>
+        <v>none</v>
       </c>
       <c r="E4" s="2" t="str">
         <v>none</v>
@@ -551,19 +597,19 @@
         <v>Nice!</v>
       </c>
       <c r="G4" s="2" t="str">
-        <v>X</v>
+        <v>none</v>
       </c>
       <c r="H4" s="2" t="str">
-        <v>X</v>
+        <v>none</v>
       </c>
       <c r="I4" s="2" t="str">
-        <v>X</v>
+        <v>none</v>
       </c>
       <c r="J4" s="2" t="str">
         <v>MA-Single</v>
       </c>
       <c r="K4" s="2" t="str">
-        <v>X</v>
+        <v>none</v>
       </c>
       <c r="L4" s="2">
         <v>750</v>
@@ -572,23 +618,29 @@
         <v>Personal Tax Services - JJ</v>
       </c>
       <c r="N4" s="2" t="str">
-        <v>X</v>
+        <v>none</v>
       </c>
       <c r="O4" s="2" t="str">
         <v>2022 1040 Return - JJ</v>
+      </c>
+      <c r="P4" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>2023</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:Q4"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="str">
@@ -636,6 +688,12 @@
       <c r="O1" s="2" t="str">
         <v>Pipeline</v>
       </c>
+      <c r="P1" s="2" t="str">
+        <v>Seal</v>
+      </c>
+      <c r="Q1" s="2" t="str">
+        <v>YearToSeal</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2">
@@ -647,28 +705,28 @@
       <c r="C2" s="2" t="str">
         <v>Single, Dummy</v>
       </c>
-      <c r="D2" s="2" t="str">
-        <v>Y</v>
-      </c>
-      <c r="E2" s="2" t="str">
+      <c r="D2" s="3" t="str">
+        <v>N</v>
+      </c>
+      <c r="E2" s="4" t="str">
         <v>N</v>
       </c>
       <c r="F2" s="2" t="str">
         <v>Nice!</v>
       </c>
-      <c r="G2" s="2" t="str">
-        <v>N</v>
-      </c>
-      <c r="H2" s="2" t="str">
-        <v>N</v>
-      </c>
-      <c r="I2" s="2" t="str">
+      <c r="G2" s="4" t="str">
+        <v>N</v>
+      </c>
+      <c r="H2" s="4" t="str">
+        <v>N</v>
+      </c>
+      <c r="I2" s="4" t="str">
         <v>N</v>
       </c>
       <c r="J2" s="2" t="str">
         <v>MA-Single</v>
       </c>
-      <c r="K2" s="2" t="str">
+      <c r="K2" s="4" t="str">
         <v>N</v>
       </c>
       <c r="L2" s="2">
@@ -677,11 +735,17 @@
       <c r="M2" s="2" t="str">
         <v>Personal Tax Services - JJ</v>
       </c>
-      <c r="N2" s="2" t="str">
-        <v>Y</v>
+      <c r="N2" s="4" t="str">
+        <v>N</v>
       </c>
       <c r="O2" s="2" t="str">
         <v>2022 1040 Return - JJ</v>
+      </c>
+      <c r="P2" s="5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>2023</v>
       </c>
     </row>
     <row r="3">
@@ -694,29 +758,29 @@
       <c r="C3" s="2" t="str">
         <v>DummyDiffLastName, Married &amp; WeirdDiff-LastName, Spouse</v>
       </c>
-      <c r="D3" s="2" t="str">
-        <v>Y</v>
-      </c>
-      <c r="E3" s="2" t="str">
+      <c r="D3" s="4" t="str">
+        <v>N</v>
+      </c>
+      <c r="E3" s="4" t="str">
         <v>N</v>
       </c>
       <c r="F3" s="2" t="str">
         <v>Great!</v>
       </c>
       <c r="G3" s="2" t="str">
-        <v>Y</v>
+        <v>none</v>
       </c>
       <c r="H3" s="2" t="str">
-        <v>Y</v>
+        <v>none</v>
       </c>
       <c r="I3" s="2" t="str">
-        <v>N</v>
+        <v>none</v>
       </c>
       <c r="J3" s="2" t="str">
         <v>MA-Single</v>
       </c>
-      <c r="K3" s="2" t="str">
-        <v>Y</v>
+      <c r="K3" s="4" t="str">
+        <v>N</v>
       </c>
       <c r="L3" s="2">
         <v>1000</v>
@@ -724,11 +788,17 @@
       <c r="M3" s="2" t="str">
         <v>Personal Tax Services - JJ</v>
       </c>
-      <c r="N3" s="2" t="str">
-        <v>Y</v>
+      <c r="N3" s="4" t="str">
+        <v>N</v>
       </c>
       <c r="O3" s="2" t="str">
         <v>2022 1040 Return - JJ</v>
+      </c>
+      <c r="P3" s="6" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>2023</v>
       </c>
     </row>
     <row r="4">
@@ -741,29 +811,29 @@
       <c r="C4" s="2" t="str">
         <v>Single, Dummy</v>
       </c>
-      <c r="D4" s="2" t="str">
-        <v>Send CRM Code</v>
-      </c>
-      <c r="E4" s="2" t="str">
-        <v>none</v>
+      <c r="D4" s="4" t="str">
+        <v>N</v>
+      </c>
+      <c r="E4" s="4" t="str">
+        <v>N</v>
       </c>
       <c r="F4" s="2" t="str">
         <v>Nice!</v>
       </c>
-      <c r="G4" s="2" t="str">
-        <v>X</v>
-      </c>
-      <c r="H4" s="2" t="str">
-        <v>X</v>
-      </c>
-      <c r="I4" s="2" t="str">
-        <v>X</v>
+      <c r="G4" s="4" t="str">
+        <v>N</v>
+      </c>
+      <c r="H4" s="4" t="str">
+        <v>N</v>
+      </c>
+      <c r="I4" s="4" t="str">
+        <v>N</v>
       </c>
       <c r="J4" s="2" t="str">
         <v>MA-Single</v>
       </c>
-      <c r="K4" s="2" t="str">
-        <v>X</v>
+      <c r="K4" s="4" t="str">
+        <v>N</v>
       </c>
       <c r="L4" s="2">
         <v>750</v>
@@ -771,16 +841,22 @@
       <c r="M4" s="2" t="str">
         <v>Personal Tax Services - JJ</v>
       </c>
-      <c r="N4" s="2" t="str">
-        <v>X</v>
+      <c r="N4" s="4" t="str">
+        <v>N</v>
       </c>
       <c r="O4" s="2" t="str">
         <v>2022 1040 Return - JJ</v>
+      </c>
+      <c r="P4" s="6" t="str">
+        <v>Y</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>2023</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/AutomateSendingOutTaxReturnsV3.xlsx
+++ b/AutomateSendingOutTaxReturnsV3.xlsx
@@ -497,7 +497,7 @@
         <v>none</v>
       </c>
       <c r="I2" s="2" t="str">
-        <v>none</v>
+        <v>X</v>
       </c>
       <c r="J2" s="2" t="str">
         <v>MA-Single</v>
@@ -518,7 +518,7 @@
         <v>2022 1040 Return - JJ</v>
       </c>
       <c r="P2" s="2" t="str">
-        <v>X</v>
+        <v>none</v>
       </c>
       <c r="Q2" s="2">
         <v>2023</v>
@@ -550,7 +550,7 @@
         <v>none</v>
       </c>
       <c r="I3" s="2" t="str">
-        <v>none</v>
+        <v>X</v>
       </c>
       <c r="J3" s="2" t="str">
         <v>MA-Single</v>
@@ -571,7 +571,7 @@
         <v>2022 1040 Return - JJ</v>
       </c>
       <c r="P3" s="2" t="str">
-        <v>X</v>
+        <v>none</v>
       </c>
       <c r="Q3" s="2">
         <v>2023</v>
@@ -603,7 +603,7 @@
         <v>none</v>
       </c>
       <c r="I4" s="2" t="str">
-        <v>none</v>
+        <v>X</v>
       </c>
       <c r="J4" s="2" t="str">
         <v>MA-Single</v>
@@ -624,7 +624,7 @@
         <v>2022 1040 Return - JJ</v>
       </c>
       <c r="P4" s="2" t="str">
-        <v>X</v>
+        <v>none</v>
       </c>
       <c r="Q4" s="2">
         <v>2023</v>
@@ -720,8 +720,8 @@
       <c r="H2" s="4" t="str">
         <v>N</v>
       </c>
-      <c r="I2" s="4" t="str">
-        <v>N</v>
+      <c r="I2" s="5" t="str">
+        <v>Y</v>
       </c>
       <c r="J2" s="2" t="str">
         <v>MA-Single</v>
@@ -741,8 +741,8 @@
       <c r="O2" s="2" t="str">
         <v>2022 1040 Return - JJ</v>
       </c>
-      <c r="P2" s="5" t="str">
-        <v>Y</v>
+      <c r="P2" s="2" t="str">
+        <v>none</v>
       </c>
       <c r="Q2" s="2">
         <v>2023</v>
@@ -767,14 +767,14 @@
       <c r="F3" s="2" t="str">
         <v>Great!</v>
       </c>
-      <c r="G3" s="2" t="str">
-        <v>none</v>
-      </c>
-      <c r="H3" s="2" t="str">
-        <v>none</v>
-      </c>
-      <c r="I3" s="2" t="str">
-        <v>none</v>
+      <c r="G3" s="4" t="str">
+        <v>N</v>
+      </c>
+      <c r="H3" s="4" t="str">
+        <v>N</v>
+      </c>
+      <c r="I3" s="6" t="str">
+        <v>Y</v>
       </c>
       <c r="J3" s="2" t="str">
         <v>MA-Single</v>
@@ -794,8 +794,8 @@
       <c r="O3" s="2" t="str">
         <v>2022 1040 Return - JJ</v>
       </c>
-      <c r="P3" s="6" t="str">
-        <v>Y</v>
+      <c r="P3" s="2" t="str">
+        <v>none</v>
       </c>
       <c r="Q3" s="2">
         <v>2023</v>
@@ -826,8 +826,8 @@
       <c r="H4" s="4" t="str">
         <v>N</v>
       </c>
-      <c r="I4" s="4" t="str">
-        <v>N</v>
+      <c r="I4" s="6" t="str">
+        <v>Y</v>
       </c>
       <c r="J4" s="2" t="str">
         <v>MA-Single</v>
@@ -847,8 +847,8 @@
       <c r="O4" s="2" t="str">
         <v>2022 1040 Return - JJ</v>
       </c>
-      <c r="P4" s="6" t="str">
-        <v>Y</v>
+      <c r="P4" s="2" t="str">
+        <v>none</v>
       </c>
       <c r="Q4" s="2">
         <v>2023</v>

--- a/AutomateSendingOutTaxReturnsV3.xlsx
+++ b/AutomateSendingOutTaxReturnsV3.xlsx
@@ -22,7 +22,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="2">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -30,30 +30,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125">
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -77,14 +53,10 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -416,7 +388,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:R4"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="str">
@@ -450,24 +422,27 @@
         <v>SignatureTemplate</v>
       </c>
       <c r="K1" s="2" t="str">
+        <v>RequireKBA</v>
+      </c>
+      <c r="L1" s="2" t="str">
         <v>Invoice</v>
       </c>
-      <c r="L1" s="2" t="str">
+      <c r="M1" s="2" t="str">
         <v>InvoiceAmount</v>
       </c>
-      <c r="M1" s="2" t="str">
+      <c r="N1" s="2" t="str">
         <v>InvoiceTemplate</v>
       </c>
-      <c r="N1" s="2" t="str">
+      <c r="O1" s="2" t="str">
         <v>Closer</v>
       </c>
-      <c r="O1" s="2" t="str">
+      <c r="P1" s="2" t="str">
         <v>Pipeline</v>
       </c>
-      <c r="P1" s="2" t="str">
+      <c r="Q1" s="2" t="str">
         <v>Seal</v>
       </c>
-      <c r="Q1" s="2" t="str">
+      <c r="R1" s="2" t="str">
         <v>YearToSeal</v>
       </c>
     </row>
@@ -505,22 +480,25 @@
       <c r="K2" s="2" t="str">
         <v>none</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="M2" s="2">
         <v>750</v>
       </c>
-      <c r="M2" s="2" t="str">
+      <c r="N2" s="2" t="str">
         <v>Personal Tax Services - JJ</v>
       </c>
-      <c r="N2" s="2" t="str">
-        <v>none</v>
-      </c>
       <c r="O2" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="P2" s="2" t="str">
         <v>2022 1040 Return - JJ</v>
       </c>
-      <c r="P2" s="2" t="str">
-        <v>none</v>
-      </c>
-      <c r="Q2" s="2">
+      <c r="Q2" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="R2" s="2">
         <v>2023</v>
       </c>
     </row>
@@ -553,27 +531,30 @@
         <v>X</v>
       </c>
       <c r="J3" s="2" t="str">
-        <v>MA-Single</v>
+        <v>none</v>
       </c>
       <c r="K3" s="2" t="str">
-        <v>none</v>
-      </c>
-      <c r="L3" s="2">
+        <v>X</v>
+      </c>
+      <c r="L3" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="M3" s="2">
         <v>1000</v>
       </c>
-      <c r="M3" s="2" t="str">
+      <c r="N3" s="2" t="str">
         <v>Personal Tax Services - JJ</v>
       </c>
-      <c r="N3" s="2" t="str">
-        <v>none</v>
-      </c>
       <c r="O3" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="P3" s="2" t="str">
         <v>2022 1040 Return - JJ</v>
       </c>
-      <c r="P3" s="2" t="str">
-        <v>none</v>
-      </c>
-      <c r="Q3" s="2">
+      <c r="Q3" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="R3" s="2">
         <v>2023</v>
       </c>
     </row>
@@ -609,254 +590,44 @@
         <v>MA-Single</v>
       </c>
       <c r="K4" s="2" t="str">
-        <v>none</v>
-      </c>
-      <c r="L4" s="2">
+        <v>X</v>
+      </c>
+      <c r="L4" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="M4" s="2">
         <v>750</v>
       </c>
-      <c r="M4" s="2" t="str">
+      <c r="N4" s="2" t="str">
         <v>Personal Tax Services - JJ</v>
       </c>
-      <c r="N4" s="2" t="str">
-        <v>none</v>
-      </c>
       <c r="O4" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="P4" s="2" t="str">
         <v>2022 1040 Return - JJ</v>
       </c>
-      <c r="P4" s="2" t="str">
-        <v>none</v>
-      </c>
-      <c r="Q4" s="2">
+      <c r="Q4" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="R4" s="2">
         <v>2023</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q4"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="str">
-        <v>Number</v>
-      </c>
-      <c r="B1" s="2" t="str">
-        <v>ClientID</v>
-      </c>
-      <c r="C1" s="2" t="str">
-        <v>ClientName</v>
-      </c>
-      <c r="D1" s="2" t="str">
-        <v>EmailTemp1</v>
-      </c>
-      <c r="E1" s="2" t="str">
-        <v>EmailTemp2</v>
-      </c>
-      <c r="F1" s="2" t="str">
-        <v>Comment</v>
-      </c>
-      <c r="G1" s="2" t="str">
-        <v>Estimate</v>
-      </c>
-      <c r="H1" s="2" t="str">
-        <v>TaxReturn</v>
-      </c>
-      <c r="I1" s="2" t="str">
-        <v>Signature</v>
-      </c>
-      <c r="J1" s="2" t="str">
-        <v>SignatureTemplate</v>
-      </c>
-      <c r="K1" s="2" t="str">
-        <v>Invoice</v>
-      </c>
-      <c r="L1" s="2" t="str">
-        <v>InvoiceAmount</v>
-      </c>
-      <c r="M1" s="2" t="str">
-        <v>InvoiceTemplate</v>
-      </c>
-      <c r="N1" s="2" t="str">
-        <v>Closer</v>
-      </c>
-      <c r="O1" s="2" t="str">
-        <v>Pipeline</v>
-      </c>
-      <c r="P1" s="2" t="str">
-        <v>Seal</v>
-      </c>
-      <c r="Q1" s="2" t="str">
-        <v>YearToSeal</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="str">
-        <v>SD3</v>
-      </c>
-      <c r="C2" s="2" t="str">
-        <v>Single, Dummy</v>
-      </c>
-      <c r="D2" s="3" t="str">
-        <v>N</v>
-      </c>
-      <c r="E2" s="4" t="str">
-        <v>N</v>
-      </c>
-      <c r="F2" s="2" t="str">
-        <v>Nice!</v>
-      </c>
-      <c r="G2" s="4" t="str">
-        <v>N</v>
-      </c>
-      <c r="H2" s="4" t="str">
-        <v>N</v>
-      </c>
-      <c r="I2" s="5" t="str">
-        <v>Y</v>
-      </c>
-      <c r="J2" s="2" t="str">
-        <v>MA-Single</v>
-      </c>
-      <c r="K2" s="4" t="str">
-        <v>N</v>
-      </c>
-      <c r="L2" s="2">
-        <v>750</v>
-      </c>
-      <c r="M2" s="2" t="str">
-        <v>Personal Tax Services - JJ</v>
-      </c>
-      <c r="N2" s="4" t="str">
-        <v>N</v>
-      </c>
-      <c r="O2" s="2" t="str">
-        <v>2022 1040 Return - JJ</v>
-      </c>
-      <c r="P2" s="2" t="str">
-        <v>none</v>
-      </c>
-      <c r="Q2" s="2">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="str">
-        <v>DM13</v>
-      </c>
-      <c r="C3" s="2" t="str">
-        <v>DummyDiffLastName, Married &amp; WeirdDiff-LastName, Spouse</v>
-      </c>
-      <c r="D3" s="4" t="str">
-        <v>N</v>
-      </c>
-      <c r="E3" s="4" t="str">
-        <v>N</v>
-      </c>
-      <c r="F3" s="2" t="str">
-        <v>Great!</v>
-      </c>
-      <c r="G3" s="4" t="str">
-        <v>N</v>
-      </c>
-      <c r="H3" s="4" t="str">
-        <v>N</v>
-      </c>
-      <c r="I3" s="6" t="str">
-        <v>Y</v>
-      </c>
-      <c r="J3" s="2" t="str">
-        <v>MA-Single</v>
-      </c>
-      <c r="K3" s="4" t="str">
-        <v>N</v>
-      </c>
-      <c r="L3" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M3" s="2" t="str">
-        <v>Personal Tax Services - JJ</v>
-      </c>
-      <c r="N3" s="4" t="str">
-        <v>N</v>
-      </c>
-      <c r="O3" s="2" t="str">
-        <v>2022 1040 Return - JJ</v>
-      </c>
-      <c r="P3" s="2" t="str">
-        <v>none</v>
-      </c>
-      <c r="Q3" s="2">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="str">
-        <v>SD3</v>
-      </c>
-      <c r="C4" s="2" t="str">
-        <v>Single, Dummy</v>
-      </c>
-      <c r="D4" s="4" t="str">
-        <v>N</v>
-      </c>
-      <c r="E4" s="4" t="str">
-        <v>N</v>
-      </c>
-      <c r="F4" s="2" t="str">
-        <v>Nice!</v>
-      </c>
-      <c r="G4" s="4" t="str">
-        <v>N</v>
-      </c>
-      <c r="H4" s="4" t="str">
-        <v>N</v>
-      </c>
-      <c r="I4" s="6" t="str">
-        <v>Y</v>
-      </c>
-      <c r="J4" s="2" t="str">
-        <v>MA-Single</v>
-      </c>
-      <c r="K4" s="4" t="str">
-        <v>N</v>
-      </c>
-      <c r="L4" s="2">
-        <v>750</v>
-      </c>
-      <c r="M4" s="2" t="str">
-        <v>Personal Tax Services - JJ</v>
-      </c>
-      <c r="N4" s="4" t="str">
-        <v>N</v>
-      </c>
-      <c r="O4" s="2" t="str">
-        <v>2022 1040 Return - JJ</v>
-      </c>
-      <c r="P4" s="2" t="str">
-        <v>none</v>
-      </c>
-      <c r="Q4" s="2">
-        <v>2023</v>
-      </c>
-    </row>
-  </sheetData>
+  <dimension ref="A1"/>
+  <sheetData/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/AutomateSendingOutTaxReturnsV3.xlsx
+++ b/AutomateSendingOutTaxReturnsV3.xlsx
@@ -1,47 +1,155 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook" filterPrivacy="true"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0BD0418-98D9-4B69-93E9-0F4B88538018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="ClientList" sheetId="1" r:id="rId1"/>
     <sheet name="ClientSummary" sheetId="2" r:id="rId2"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="31">
+  <si>
+    <t>Number</t>
+  </si>
+  <si>
+    <t>ClientID</t>
+  </si>
+  <si>
+    <t>ClientName</t>
+  </si>
+  <si>
+    <t>EmailTemp1</t>
+  </si>
+  <si>
+    <t>EmailTemp2</t>
+  </si>
+  <si>
+    <t>Comment</t>
+  </si>
+  <si>
+    <t>Estimate</t>
+  </si>
+  <si>
+    <t>TaxReturn</t>
+  </si>
+  <si>
+    <t>Signature</t>
+  </si>
+  <si>
+    <t>SignatureTemplate</t>
+  </si>
+  <si>
+    <t>RequireKBA</t>
+  </si>
+  <si>
+    <t>Invoice</t>
+  </si>
+  <si>
+    <t>InvoiceAmount</t>
+  </si>
+  <si>
+    <t>InvoiceTemplate</t>
+  </si>
+  <si>
+    <t>Closer</t>
+  </si>
+  <si>
+    <t>Pipeline</t>
+  </si>
+  <si>
+    <t>Seal</t>
+  </si>
+  <si>
+    <t>YearToSeal</t>
+  </si>
+  <si>
+    <t>SD3</t>
+  </si>
+  <si>
+    <t>Single, Dummy</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>Put the comment in that I type out for them.  It’s a comment on their tax return</t>
+  </si>
+  <si>
+    <t>MA-Single</t>
+  </si>
+  <si>
+    <t>Personal Tax Services - JJ</t>
+  </si>
+  <si>
+    <t>2022 1040 Return - JJ</t>
+  </si>
+  <si>
+    <t>DM13</t>
+  </si>
+  <si>
+    <t>DummyDiffLastName, Married &amp; WeirdDiff-LastName, Spouse</t>
+  </si>
+  <si>
+    <t>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Praesent aliquet, magna ut molestie venenatis, felis mauris ultricies augue, a commodo nisl nisi at sapien. Proin vulputate erat a pharetra tempor. Nam tellus nisi, scelerisque ac molestie eleifend, pellentesque tempus mi. Sed ullamcorper cursus lacinia. Cras maximus diam velit, nec efficitur dui auctor eget. Vivamus porttitor ultricies ante, nec elementum leo porttitor non. Nam aliquet velit purus, a luctus purus varius at. Integer at urna a turpis blandit dapibus. Nulla auctor imperdiet massa, ac pretium lorem lobortis sollicitudin. Nullam felis turpis, molestie nec vestibulum in, dapibus et turpis.</t>
+  </si>
+  <si>
+    <t>Aliquam urna tortor, eleifend quis lorem sed, faucibus accumsan nulla. Nam luctus erat velit, quis elementum urna luctus vitae. Praesent consectetur, nisi sed mattis volutpat, nunc risus ullamcorper sem, eu pulvinar orci ante elementum ante. Cras cursus turpis in ligula volutpat maximus. Vestibulum ut porta justo, ac mattis tortor. Proin consequat sapien nec turpis mattis, vitae consequat risus convallis. Nulla laoreet volutpat iaculis. Aenean suscipit, leo a volutpat aliquet, massa sapien faucibus nisl, imperdiet consectetur lectus augue id nunc. Mauris nunc lectus, pharetra sit amet ligula sit amet, rhoncus imperdiet lacus. Maecenas faucibus facilisis odio nec varius. Aliquam ut sem leo. Duis dui ligula, commodo sed ligula at, imperdiet mollis felis. Nam ut semper enim. Nulla at ultricies metus. Nulla ut massa in lectus lacinia varius sit amet vitae ex. Ut laoreet interdum nisi in laoreet.</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
-  <fonts count="2" x14ac:knownFonts="1">
-    <font>
-      <sz val="12"/>
-      <name val="Calibri"/>
-    </font>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
-      <patternFill patternType="none">
-        <bgColor/>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <bgColor/>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FF00"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -50,19 +158,29 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs>
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -387,247 +505,478 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="str">
-        <v>Number</v>
-      </c>
-      <c r="B1" s="2" t="str">
-        <v>ClientID</v>
-      </c>
-      <c r="C1" s="2" t="str">
-        <v>ClientName</v>
-      </c>
-      <c r="D1" s="2" t="str">
-        <v>EmailTemp1</v>
-      </c>
-      <c r="E1" s="2" t="str">
-        <v>EmailTemp2</v>
-      </c>
-      <c r="F1" s="2" t="str">
-        <v>Comment</v>
-      </c>
-      <c r="G1" s="2" t="str">
-        <v>Estimate</v>
-      </c>
-      <c r="H1" s="2" t="str">
-        <v>TaxReturn</v>
-      </c>
-      <c r="I1" s="2" t="str">
-        <v>Signature</v>
-      </c>
-      <c r="J1" s="2" t="str">
-        <v>SignatureTemplate</v>
-      </c>
-      <c r="K1" s="2" t="str">
-        <v>RequireKBA</v>
-      </c>
-      <c r="L1" s="2" t="str">
-        <v>Invoice</v>
-      </c>
-      <c r="M1" s="2" t="str">
-        <v>InvoiceAmount</v>
-      </c>
-      <c r="N1" s="2" t="str">
-        <v>InvoiceTemplate</v>
-      </c>
-      <c r="O1" s="2" t="str">
-        <v>Closer</v>
-      </c>
-      <c r="P1" s="2" t="str">
-        <v>Pipeline</v>
-      </c>
-      <c r="Q1" s="2" t="str">
-        <v>Seal</v>
-      </c>
-      <c r="R1" s="2" t="str">
-        <v>YearToSeal</v>
+    <row r="1" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2">
+    <row r="2" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="str">
-        <v>SD3</v>
-      </c>
-      <c r="C2" s="2" t="str">
-        <v>Single, Dummy</v>
-      </c>
-      <c r="D2" s="2" t="str">
-        <v>none</v>
-      </c>
-      <c r="E2" s="2" t="str">
-        <v>none</v>
-      </c>
-      <c r="F2" s="2" t="str">
-        <v>Nice!</v>
-      </c>
-      <c r="G2" s="2" t="str">
-        <v>none</v>
-      </c>
-      <c r="H2" s="2" t="str">
-        <v>none</v>
-      </c>
-      <c r="I2" s="2" t="str">
-        <v>X</v>
-      </c>
-      <c r="J2" s="2" t="str">
-        <v>MA-Single</v>
-      </c>
-      <c r="K2" s="2" t="str">
-        <v>none</v>
-      </c>
-      <c r="L2" s="2" t="str">
-        <v>none</v>
-      </c>
-      <c r="M2" s="2">
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2">
         <v>750</v>
       </c>
-      <c r="N2" s="2" t="str">
-        <v>Personal Tax Services - JJ</v>
-      </c>
-      <c r="O2" s="2" t="str">
-        <v>none</v>
-      </c>
-      <c r="P2" s="2" t="str">
-        <v>2022 1040 Return - JJ</v>
-      </c>
-      <c r="Q2" s="2" t="str">
-        <v>none</v>
-      </c>
-      <c r="R2" s="2">
+      <c r="N2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R2">
         <v>2023</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2">
+    <row r="3" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="str">
-        <v>DM13</v>
-      </c>
-      <c r="C3" s="2" t="str">
-        <v>DummyDiffLastName, Married &amp; WeirdDiff-LastName, Spouse</v>
-      </c>
-      <c r="D3" s="2" t="str">
-        <v>none</v>
-      </c>
-      <c r="E3" s="2" t="str">
-        <v>none</v>
-      </c>
-      <c r="F3" s="2" t="str">
-        <v>Great!</v>
-      </c>
-      <c r="G3" s="2" t="str">
-        <v>none</v>
-      </c>
-      <c r="H3" s="2" t="str">
-        <v>none</v>
-      </c>
-      <c r="I3" s="2" t="str">
-        <v>X</v>
-      </c>
-      <c r="J3" s="2" t="str">
-        <v>none</v>
-      </c>
-      <c r="K3" s="2" t="str">
-        <v>X</v>
-      </c>
-      <c r="L3" s="2" t="str">
-        <v>none</v>
-      </c>
-      <c r="M3" s="2">
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M3">
         <v>1000</v>
       </c>
-      <c r="N3" s="2" t="str">
-        <v>Personal Tax Services - JJ</v>
-      </c>
-      <c r="O3" s="2" t="str">
-        <v>none</v>
-      </c>
-      <c r="P3" s="2" t="str">
-        <v>2022 1040 Return - JJ</v>
-      </c>
-      <c r="Q3" s="2" t="str">
-        <v>none</v>
-      </c>
-      <c r="R3" s="2">
+      <c r="N3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R3">
         <v>2023</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2">
+    <row r="4" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="str">
-        <v>SD3</v>
-      </c>
-      <c r="C4" s="2" t="str">
-        <v>Single, Dummy</v>
-      </c>
-      <c r="D4" s="2" t="str">
-        <v>none</v>
-      </c>
-      <c r="E4" s="2" t="str">
-        <v>none</v>
-      </c>
-      <c r="F4" s="2" t="str">
-        <v>Nice!</v>
-      </c>
-      <c r="G4" s="2" t="str">
-        <v>none</v>
-      </c>
-      <c r="H4" s="2" t="str">
-        <v>none</v>
-      </c>
-      <c r="I4" s="2" t="str">
-        <v>X</v>
-      </c>
-      <c r="J4" s="2" t="str">
-        <v>MA-Single</v>
-      </c>
-      <c r="K4" s="2" t="str">
-        <v>X</v>
-      </c>
-      <c r="L4" s="2" t="str">
-        <v>none</v>
-      </c>
-      <c r="M4" s="2">
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M4">
         <v>750</v>
       </c>
-      <c r="N4" s="2" t="str">
-        <v>Personal Tax Services - JJ</v>
-      </c>
-      <c r="O4" s="2" t="str">
-        <v>none</v>
-      </c>
-      <c r="P4" s="2" t="str">
-        <v>2022 1040 Return - JJ</v>
-      </c>
-      <c r="Q4" s="2" t="str">
-        <v>none</v>
-      </c>
-      <c r="R4" s="2">
+      <c r="N4" t="s">
+        <v>23</v>
+      </c>
+      <c r="O4" t="s">
+        <v>20</v>
+      </c>
+      <c r="P4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>20</v>
+      </c>
+      <c r="R4">
         <v>2023</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R4"/>
+    <ignoredError sqref="A1:R5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:R4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="4" max="5" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2">
+        <v>750</v>
+      </c>
+      <c r="N2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R2">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3">
+        <v>1000</v>
+      </c>
+      <c r="N3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R3">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M4">
+        <v>750</v>
+      </c>
+      <c r="N4" t="s">
+        <v>23</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>20</v>
+      </c>
+      <c r="R4">
+        <v>2023</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError sqref="A1:R4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/AutomateSendingOutTaxReturnsV3.xlsx
+++ b/AutomateSendingOutTaxReturnsV3.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0BD0418-98D9-4B69-93E9-0F4B88538018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3C1D12E-AAD6-4B6F-B621-C59ACA47EFCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -140,12 +140,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor rgb="FF00FF00"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
+        <fgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -736,7 +736,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:R5" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:R1 A4:D4 A2:D2 F2:R2 A3:D3 F3:R3 F4:R4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -745,9 +745,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="4" max="5" width="11" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -821,16 +818,16 @@
       <c r="E2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I2" s="3" t="s">
+      <c r="F2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>29</v>
       </c>
       <c r="J2" t="s">
@@ -839,7 +836,7 @@
       <c r="K2" t="s">
         <v>20</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="4" t="s">
         <v>29</v>
       </c>
       <c r="M2">
@@ -848,7 +845,7 @@
       <c r="N2" t="s">
         <v>23</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="O2" s="4" t="s">
         <v>29</v>
       </c>
       <c r="P2" t="s">
@@ -871,22 +868,22 @@
       <c r="C3" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" s="4" t="s">
+      <c r="D3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I3" s="3" t="s">
+      <c r="F3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" s="4" t="s">
         <v>29</v>
       </c>
       <c r="J3" t="s">
@@ -895,7 +892,7 @@
       <c r="K3" t="s">
         <v>20</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="4" t="s">
         <v>29</v>
       </c>
       <c r="M3">
@@ -904,7 +901,7 @@
       <c r="N3" t="s">
         <v>23</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="O3" s="4" t="s">
         <v>29</v>
       </c>
       <c r="P3" t="s">
@@ -927,22 +924,22 @@
       <c r="C4" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="G4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="4" t="s">
         <v>29</v>
       </c>
       <c r="J4" t="s">
@@ -951,7 +948,7 @@
       <c r="K4" t="s">
         <v>20</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="L4" s="4" t="s">
         <v>29</v>
       </c>
       <c r="M4">
@@ -960,7 +957,7 @@
       <c r="N4" t="s">
         <v>23</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="O4" s="4" t="s">
         <v>29</v>
       </c>
       <c r="P4" t="s">

--- a/AutomateSendingOutTaxReturnsV3.xlsx
+++ b/AutomateSendingOutTaxReturnsV3.xlsx
@@ -22,7 +22,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -42,12 +42,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -77,14 +71,13 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -509,7 +502,7 @@
         <v>none</v>
       </c>
       <c r="L2" s="2" t="str">
-        <v>create</v>
+        <v>none</v>
       </c>
       <c r="M2" s="2">
         <v>750</v>
@@ -518,7 +511,7 @@
         <v>Personal Tax Services - JJ</v>
       </c>
       <c r="O2" s="2" t="str">
-        <v>none</v>
+        <v>X</v>
       </c>
       <c r="P2" s="2" t="str">
         <v>2022 1040 Return - JJ</v>
@@ -565,7 +558,7 @@
         <v>none</v>
       </c>
       <c r="L3" s="2" t="str">
-        <v>create</v>
+        <v>none</v>
       </c>
       <c r="M3" s="2">
         <v>1000</v>
@@ -574,7 +567,7 @@
         <v>Personal Tax Services - JJ</v>
       </c>
       <c r="O3" s="2" t="str">
-        <v>none</v>
+        <v>X</v>
       </c>
       <c r="P3" s="2" t="str">
         <v>2022 1040 Return - JJ</v>
@@ -621,7 +614,7 @@
         <v>none</v>
       </c>
       <c r="L4" s="2" t="str">
-        <v>create</v>
+        <v>none</v>
       </c>
       <c r="M4" s="2">
         <v>750</v>
@@ -630,7 +623,7 @@
         <v>Personal Tax Services - JJ</v>
       </c>
       <c r="O4" s="2" t="str">
-        <v>none</v>
+        <v>X</v>
       </c>
       <c r="P4" s="2" t="str">
         <v>2022 1040 Return - JJ</v>
@@ -753,8 +746,8 @@
       <c r="N2" s="2" t="str">
         <v>Personal Tax Services - JJ</v>
       </c>
-      <c r="O2" s="4" t="str">
-        <v>N</v>
+      <c r="O2" s="5" t="str">
+        <v>Y</v>
       </c>
       <c r="P2" s="2" t="str">
         <v>2022 1040 Return - JJ</v>
@@ -785,14 +778,14 @@
       <c r="F3" s="2" t="str">
         <v>none</v>
       </c>
-      <c r="G3" s="4" t="str">
-        <v>N</v>
-      </c>
-      <c r="H3" s="4" t="str">
-        <v>N</v>
-      </c>
-      <c r="I3" s="4" t="str">
-        <v>N</v>
+      <c r="G3" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="H3" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="I3" s="2" t="str">
+        <v>none</v>
       </c>
       <c r="J3" s="2" t="str">
         <v>MA-Single</v>
@@ -800,8 +793,8 @@
       <c r="K3" s="2" t="str">
         <v>none</v>
       </c>
-      <c r="L3" s="5" t="str">
-        <v>Y</v>
+      <c r="L3" s="2" t="str">
+        <v>none</v>
       </c>
       <c r="M3" s="2">
         <v>1000</v>
@@ -841,14 +834,14 @@
       <c r="F4" s="2" t="str">
         <v>none</v>
       </c>
-      <c r="G4" s="4" t="str">
-        <v>N</v>
-      </c>
-      <c r="H4" s="4" t="str">
-        <v>N</v>
-      </c>
-      <c r="I4" s="4" t="str">
-        <v>N</v>
+      <c r="G4" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="H4" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="I4" s="2" t="str">
+        <v>none</v>
       </c>
       <c r="J4" s="2" t="str">
         <v>MA-Single</v>
@@ -856,8 +849,8 @@
       <c r="K4" s="2" t="str">
         <v>none</v>
       </c>
-      <c r="L4" s="6" t="str">
-        <v>Y</v>
+      <c r="L4" s="2" t="str">
+        <v>none</v>
       </c>
       <c r="M4" s="2">
         <v>750</v>

--- a/AutomateSendingOutTaxReturnsV3.xlsx
+++ b/AutomateSendingOutTaxReturnsV3.xlsx
@@ -504,7 +504,7 @@
         <v>none</v>
       </c>
       <c r="L2" s="2" t="str">
-        <v>X</v>
+        <v>none</v>
       </c>
       <c r="M2" s="2">
         <v>750</v>
@@ -519,7 +519,7 @@
         <v>2022 1040 Return - JJ</v>
       </c>
       <c r="Q2" s="2" t="str">
-        <v>X</v>
+        <v>none</v>
       </c>
       <c r="R2" s="2">
         <v>2019</v>
@@ -642,8 +642,8 @@
       <c r="P2" s="2" t="str">
         <v>2022 1040 Return - JJ</v>
       </c>
-      <c r="Q2" s="4" t="str">
-        <v>N</v>
+      <c r="Q2" s="2" t="str">
+        <v>none</v>
       </c>
       <c r="R2" s="2">
         <v>2019</v>

--- a/AutomateSendingOutTaxReturnsV3.xlsx
+++ b/AutomateSendingOutTaxReturnsV3.xlsx
@@ -24,7 +24,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -44,6 +44,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FF00"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -73,13 +79,14 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -486,7 +493,7 @@
         <v>none</v>
       </c>
       <c r="F2" s="2" t="str">
-        <v>none</v>
+        <v>Hello</v>
       </c>
       <c r="G2" s="2" t="str">
         <v>none</v>
@@ -495,7 +502,7 @@
         <v>none</v>
       </c>
       <c r="I2" s="2" t="str">
-        <v>none</v>
+        <v>X</v>
       </c>
       <c r="J2" s="2" t="str">
         <v>none</v>
@@ -504,7 +511,7 @@
         <v>none</v>
       </c>
       <c r="L2" s="2" t="str">
-        <v>none</v>
+        <v>X</v>
       </c>
       <c r="M2" s="2">
         <v>750</v>
@@ -609,8 +616,8 @@
       <c r="E2" s="4" t="str">
         <v>N</v>
       </c>
-      <c r="F2" s="2" t="str">
-        <v>none</v>
+      <c r="F2" s="5" t="str">
+        <v>Y</v>
       </c>
       <c r="G2" s="4" t="str">
         <v>N</v>
@@ -618,17 +625,17 @@
       <c r="H2" s="4" t="str">
         <v>N</v>
       </c>
-      <c r="I2" s="4" t="str">
+      <c r="I2" s="6" t="str">
+        <v>Y</v>
+      </c>
+      <c r="J2" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="K2" s="4" t="str">
         <v>N</v>
       </c>
-      <c r="J2" s="2" t="str">
-        <v>none</v>
-      </c>
-      <c r="K2" s="2" t="str">
-        <v>none</v>
-      </c>
-      <c r="L2" s="4" t="str">
-        <v>N</v>
+      <c r="L2" s="6" t="str">
+        <v>Y</v>
       </c>
       <c r="M2" s="2">
         <v>750</v>
@@ -636,7 +643,7 @@
       <c r="N2" s="2" t="str">
         <v>Personal Tax Services - JJ</v>
       </c>
-      <c r="O2" s="5" t="str">
+      <c r="O2" s="6" t="str">
         <v>Y</v>
       </c>
       <c r="P2" s="2" t="str">

--- a/AutomateSendingOutTaxReturnsV3.xlsx
+++ b/AutomateSendingOutTaxReturnsV3.xlsx
@@ -24,7 +24,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -37,7 +37,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor rgb="FF00FF00"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -55,7 +55,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -79,7 +91,7 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -87,6 +99,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -418,7 +432,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R7"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="str">
@@ -481,25 +495,25 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="str">
-        <v>SD3</v>
+        <v>BC7</v>
       </c>
       <c r="C2" s="2" t="str">
-        <v>Single, Dummy</v>
+        <v>Brennan, Christopher &amp; Anne</v>
       </c>
       <c r="D2" s="2" t="str">
-        <v>none</v>
+        <v>Send Out Returns, Bill, and Efile Sigs - InvoiceInTD</v>
       </c>
       <c r="E2" s="2" t="str">
         <v>none</v>
       </c>
       <c r="F2" s="2" t="str">
-        <v>Hello</v>
+        <v>You owe a bit due to a BIG gain on your Vertex share sales (a good thing of course except now when you have to pay taxes on it!).  The gain is taxed at the most favorable long term capital gains rate and we adjusted your cost basis so you weren’t double taxed.  Everything else was very similar to last year.  Hope you are well - let me know if any questions - thanks!</v>
       </c>
       <c r="G2" s="2" t="str">
-        <v>none</v>
+        <v>X</v>
       </c>
       <c r="H2" s="2" t="str">
-        <v>none</v>
+        <v>X</v>
       </c>
       <c r="I2" s="2" t="str">
         <v>X</v>
@@ -508,7 +522,7 @@
         <v>none</v>
       </c>
       <c r="K2" s="2" t="str">
-        <v>none</v>
+        <v>X</v>
       </c>
       <c r="L2" s="2" t="str">
         <v>X</v>
@@ -523,26 +537,306 @@
         <v>X</v>
       </c>
       <c r="P2" s="2" t="str">
-        <v>2022 1040 Return - JJ</v>
+        <v>2023 1040 Return - JJ</v>
       </c>
       <c r="Q2" s="2" t="str">
-        <v>none</v>
+        <v>X</v>
       </c>
       <c r="R2" s="2">
-        <v>2019</v>
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="str">
+        <v>WM8</v>
+      </c>
+      <c r="C3" s="2" t="str">
+        <v>Walsh, Mary</v>
+      </c>
+      <c r="D3" s="2" t="str">
+        <v>Send Out Returns, Bill, and Efile Sigs - InvoiceInTD</v>
+      </c>
+      <c r="E3" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="F3" s="2" t="str">
+        <v>Your mother had good withholdings and thus the estate is getting a great federal refund.  Additionally there is a nice MA refund as we got $887 for the MA Senior Circuit Breaker Credit.  My condolences again on your loss - let me know if any questions - thanks.</v>
+      </c>
+      <c r="G3" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="H3" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="I3" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="J3" s="2" t="str">
+        <v>MA-Single-TS</v>
+      </c>
+      <c r="K3" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="L3" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="M3" s="2">
+        <v>900</v>
+      </c>
+      <c r="N3" s="2" t="str">
+        <v>Personal Tax Services - JJ</v>
+      </c>
+      <c r="O3" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="P3" s="2" t="str">
+        <v>2023 1040 Return - JJ</v>
+      </c>
+      <c r="Q3" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="R3" s="2">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="str">
+        <v>KS3</v>
+      </c>
+      <c r="C4" s="2" t="str">
+        <v>Kelleher, Stephen</v>
+      </c>
+      <c r="D4" s="2" t="str">
+        <v>Send Out Returns, Bill, and Efile Sigs - InvoiceInTD</v>
+      </c>
+      <c r="E4" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="F4" s="2" t="str">
+        <v>Nice increase in your rental income of $7k and another $7k increase in interest and dividends has you owing a bit as compared to last year but it’s for good reasons!  Again the rental is also the reason why you owe in RI. Glad to see you are still doing the ESPP hopefully that works out for you in the long term.  Hope you are well and as always - please let me know if you have any questions - thanks.</v>
+      </c>
+      <c r="G4" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="H4" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="I4" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="J4" s="2" t="str">
+        <v>MA-Single-TS</v>
+      </c>
+      <c r="K4" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="L4" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="M4" s="2">
+        <v>750</v>
+      </c>
+      <c r="N4" s="2" t="str">
+        <v>Personal Tax Services - JJ</v>
+      </c>
+      <c r="O4" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="P4" s="2" t="str">
+        <v>2023 1040 Return - JJ</v>
+      </c>
+      <c r="Q4" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="R4" s="2">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="str">
+        <v>ST2</v>
+      </c>
+      <c r="C5" s="2" t="str">
+        <v>Sasaki, Tomoaki</v>
+      </c>
+      <c r="D5" s="2" t="str">
+        <v>Send Out Returns, Bill, and Efile Sigs - InvoiceInTD</v>
+      </c>
+      <c r="E5" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="F5" s="2" t="str">
+        <v>You owe a little this year as your wages went up almost $6k and your withholdings went down by $3k from last year.  We noted your backdoor Roth contribution of $6,500 and excluded that in the conversion to a Roth.  Last year we noted your $6k contribution and used it to exclude taxation on the $20k IRA conversion giving you an upfront tax break so that $6k is now taxable this year.  As you are now caught up and only converting $6,500 each year there will be no more catchups or taxable contributions going forward. Let me know if any questions - thanks and hope all is well!</v>
+      </c>
+      <c r="G5" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="H5" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="I5" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="J5" s="2" t="str">
+        <v>MA-Single-TS</v>
+      </c>
+      <c r="K5" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="L5" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="M5" s="2">
+        <v>875</v>
+      </c>
+      <c r="N5" s="2" t="str">
+        <v>Personal Tax Services - JJ</v>
+      </c>
+      <c r="O5" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="P5" s="2" t="str">
+        <v>2023 1040 Return - JJ</v>
+      </c>
+      <c r="Q5" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="R5" s="2">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2">
+        <v>1</v>
+      </c>
+      <c r="B6" s="2" t="str">
+        <v>PR4</v>
+      </c>
+      <c r="C6" s="2" t="str">
+        <v>Pelly, Rachel</v>
+      </c>
+      <c r="D6" s="2" t="str">
+        <v>Send Out Returns, Bill, and Efile Sigs - InvoiceInTD</v>
+      </c>
+      <c r="E6" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="F6" s="2" t="str">
+        <v>BIG refund this year again due to your wages being down a good bit (due to less stock compensation flowing through your W2 for options exercises) and lower capital gains income. Further, you got a $2600 tax credit for energy improvements due to your home renovation.  We of course made sure to deduct your mortgage interest. Everything else looked good. Please let me know if you have any questions – thanks.</v>
+      </c>
+      <c r="G6" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="H6" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="I6" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="J6" s="2" t="str">
+        <v>MA-Single-TS</v>
+      </c>
+      <c r="K6" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="L6" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="M6" s="2">
+        <v>975</v>
+      </c>
+      <c r="N6" s="2" t="str">
+        <v>Personal Tax Services - JJ</v>
+      </c>
+      <c r="O6" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="P6" s="2" t="str">
+        <v>2023 1040 Return - JJ</v>
+      </c>
+      <c r="Q6" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="R6" s="2">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2">
+        <v>1</v>
+      </c>
+      <c r="B7" s="2" t="str">
+        <v>BM11</v>
+      </c>
+      <c r="C7" s="2" t="str">
+        <v>Bildman, Mark</v>
+      </c>
+      <c r="D7" s="2" t="str">
+        <v>Send Out Returns, Bill, and Efile Sigs - InvoiceInTD</v>
+      </c>
+      <c r="E7" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="F7" s="2" t="str">
+        <v>You had some great interest and dividends this year and that is why you owe the slightest of amounts now.  That said it’s good to get interest!  My computer just completely crashed this week but the data was backed up - made me think of how you saved my bacon back in the day!  Hope all is well - let me know if any questions - thanks.</v>
+      </c>
+      <c r="G7" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="H7" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="I7" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="J7" s="2" t="str">
+        <v>MA-Single-TS</v>
+      </c>
+      <c r="K7" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="L7" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="M7" s="2">
+        <v>475</v>
+      </c>
+      <c r="N7" s="2" t="str">
+        <v>Personal Tax Services - JJ</v>
+      </c>
+      <c r="O7" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="P7" s="2" t="str">
+        <v>2023 1040 Return - JJ</v>
+      </c>
+      <c r="Q7" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="R7" s="2">
+        <v>2023</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R7"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R7"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="str">
@@ -605,13 +899,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="str">
-        <v>SD3</v>
+        <v>BC7</v>
       </c>
       <c r="C2" s="2" t="str">
-        <v>Single, Dummy</v>
+        <v>Brennan, Christopher &amp; Anne</v>
       </c>
       <c r="D2" s="3" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E2" s="4" t="str">
         <v>N</v>
@@ -619,22 +913,22 @@
       <c r="F2" s="5" t="str">
         <v>Y</v>
       </c>
-      <c r="G2" s="4" t="str">
-        <v>N</v>
-      </c>
-      <c r="H2" s="4" t="str">
-        <v>N</v>
-      </c>
-      <c r="I2" s="6" t="str">
+      <c r="G2" s="6" t="str">
+        <v>X</v>
+      </c>
+      <c r="H2" s="5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I2" s="5" t="str">
         <v>Y</v>
       </c>
       <c r="J2" s="2" t="str">
         <v>none</v>
       </c>
-      <c r="K2" s="4" t="str">
-        <v>N</v>
-      </c>
-      <c r="L2" s="6" t="str">
+      <c r="K2" s="5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="L2" s="5" t="str">
         <v>Y</v>
       </c>
       <c r="M2" s="2">
@@ -643,29 +937,309 @@
       <c r="N2" s="2" t="str">
         <v>Personal Tax Services - JJ</v>
       </c>
-      <c r="O2" s="6" t="str">
+      <c r="O2" s="5" t="str">
         <v>Y</v>
       </c>
       <c r="P2" s="2" t="str">
-        <v>2022 1040 Return - JJ</v>
-      </c>
-      <c r="Q2" s="2" t="str">
-        <v>none</v>
+        <v>2023 1040 Return - JJ</v>
+      </c>
+      <c r="Q2" s="5" t="str">
+        <v>Y</v>
       </c>
       <c r="R2" s="2">
-        <v>2019</v>
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="str">
+        <v>WM8</v>
+      </c>
+      <c r="C3" s="2" t="str">
+        <v>Walsh, Mary</v>
+      </c>
+      <c r="D3" s="5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E3" s="7" t="str">
+        <v>N</v>
+      </c>
+      <c r="F3" s="5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G3" s="8" t="str">
+        <v>X</v>
+      </c>
+      <c r="H3" s="5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I3" s="5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="J3" s="2" t="str">
+        <v>MA-Single-TS</v>
+      </c>
+      <c r="K3" s="5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="L3" s="5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M3" s="2">
+        <v>900</v>
+      </c>
+      <c r="N3" s="2" t="str">
+        <v>Personal Tax Services - JJ</v>
+      </c>
+      <c r="O3" s="5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="P3" s="2" t="str">
+        <v>2023 1040 Return - JJ</v>
+      </c>
+      <c r="Q3" s="5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="R3" s="2">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="str">
+        <v>KS3</v>
+      </c>
+      <c r="C4" s="2" t="str">
+        <v>Kelleher, Stephen</v>
+      </c>
+      <c r="D4" s="5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E4" s="7" t="str">
+        <v>N</v>
+      </c>
+      <c r="F4" s="5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G4" s="8" t="str">
+        <v>X</v>
+      </c>
+      <c r="H4" s="5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I4" s="5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="J4" s="2" t="str">
+        <v>MA-Single-TS</v>
+      </c>
+      <c r="K4" s="5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="L4" s="5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M4" s="2">
+        <v>750</v>
+      </c>
+      <c r="N4" s="2" t="str">
+        <v>Personal Tax Services - JJ</v>
+      </c>
+      <c r="O4" s="5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="P4" s="2" t="str">
+        <v>2023 1040 Return - JJ</v>
+      </c>
+      <c r="Q4" s="5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="R4" s="2">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="str">
+        <v>ST2</v>
+      </c>
+      <c r="C5" s="2" t="str">
+        <v>Sasaki, Tomoaki</v>
+      </c>
+      <c r="D5" s="5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E5" s="7" t="str">
+        <v>N</v>
+      </c>
+      <c r="F5" s="5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G5" s="8" t="str">
+        <v>X</v>
+      </c>
+      <c r="H5" s="5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I5" s="5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="J5" s="2" t="str">
+        <v>MA-Single-TS</v>
+      </c>
+      <c r="K5" s="5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="L5" s="5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M5" s="2">
+        <v>875</v>
+      </c>
+      <c r="N5" s="2" t="str">
+        <v>Personal Tax Services - JJ</v>
+      </c>
+      <c r="O5" s="5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="P5" s="2" t="str">
+        <v>2023 1040 Return - JJ</v>
+      </c>
+      <c r="Q5" s="5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="R5" s="2">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2">
+        <v>1</v>
+      </c>
+      <c r="B6" s="2" t="str">
+        <v>PR4</v>
+      </c>
+      <c r="C6" s="2" t="str">
+        <v>Pelly, Rachel</v>
+      </c>
+      <c r="D6" s="5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E6" s="7" t="str">
+        <v>N</v>
+      </c>
+      <c r="F6" s="5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G6" s="8" t="str">
+        <v>X</v>
+      </c>
+      <c r="H6" s="5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I6" s="5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="J6" s="2" t="str">
+        <v>MA-Single-TS</v>
+      </c>
+      <c r="K6" s="5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="L6" s="5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M6" s="2">
+        <v>975</v>
+      </c>
+      <c r="N6" s="2" t="str">
+        <v>Personal Tax Services - JJ</v>
+      </c>
+      <c r="O6" s="5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="P6" s="2" t="str">
+        <v>2023 1040 Return - JJ</v>
+      </c>
+      <c r="Q6" s="5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="R6" s="2">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2">
+        <v>1</v>
+      </c>
+      <c r="B7" s="2" t="str">
+        <v>BM11</v>
+      </c>
+      <c r="C7" s="2" t="str">
+        <v>Bildman, Mark</v>
+      </c>
+      <c r="D7" s="5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E7" s="7" t="str">
+        <v>N</v>
+      </c>
+      <c r="F7" s="5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G7" s="8" t="str">
+        <v>X</v>
+      </c>
+      <c r="H7" s="5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I7" s="5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="J7" s="2" t="str">
+        <v>MA-Single-TS</v>
+      </c>
+      <c r="K7" s="5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="L7" s="5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M7" s="2">
+        <v>475</v>
+      </c>
+      <c r="N7" s="2" t="str">
+        <v>Personal Tax Services - JJ</v>
+      </c>
+      <c r="O7" s="5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="P7" s="2" t="str">
+        <v>2023 1040 Return - JJ</v>
+      </c>
+      <c r="Q7" s="5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="R7" s="2">
+        <v>2023</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R7"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R9"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="str">
@@ -728,72 +1302,633 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="str">
-        <v>SD3</v>
+        <v>SF2</v>
       </c>
       <c r="C2" s="2" t="str">
-        <v>Single, Dummy</v>
+        <v>Finney, Stephen</v>
       </c>
       <c r="D2" s="2" t="str">
-        <v>none</v>
+        <v>Send Out Returns, Bill, and Efile Sigs - InvoiceInTD</v>
       </c>
       <c r="E2" s="2" t="str">
         <v>none</v>
       </c>
       <c r="F2" s="2" t="str">
-        <v>none</v>
+        <v xml:space="preserve">Big increase in income this year compared to last! Your wages almost doubled and your withholdings kept up for the most part. You owe a little but not too much considering your overall income. We noted your $6.5k backdoor Roth IRA contribution and made sure to make it non-taxable. Finally, we also made sure to file you in 2 states - MA and RI. Everything else looked good. Please let me know if any questions – thanks. </v>
       </c>
       <c r="G2" s="2" t="str">
-        <v>none</v>
+        <v>X</v>
       </c>
       <c r="H2" s="2" t="str">
-        <v>none</v>
+        <v>X</v>
       </c>
       <c r="I2" s="2" t="str">
-        <v>none</v>
+        <v>X</v>
       </c>
       <c r="J2" s="2" t="str">
-        <v>MA-Single</v>
+        <v>none</v>
       </c>
       <c r="K2" s="2" t="str">
-        <v>none</v>
+        <v>X</v>
       </c>
       <c r="L2" s="2" t="str">
-        <v>none</v>
+        <v>X</v>
       </c>
       <c r="M2" s="2">
+        <v>875</v>
+      </c>
+      <c r="N2" s="2" t="str">
+        <v>Personal Tax Services - JJ</v>
+      </c>
+      <c r="O2" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="P2" s="2" t="str">
+        <v>2023 1040 Return - JJ</v>
+      </c>
+      <c r="Q2" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="R2" s="2">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="str">
+        <v>AA1</v>
+      </c>
+      <c r="C3" s="2" t="str">
+        <v>Aiken, Kathleen &amp; Carillo, Catherine</v>
+      </c>
+      <c r="D3" s="2" t="str">
+        <v>Send Out Returns, Bill, and Efile Sigs - InvoiceInTD</v>
+      </c>
+      <c r="E3" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="F3" s="2" t="str">
+        <v>Very similar to last year income wise in nearly all respects EXCEPT for your gambling winnings  – nice! It lowered your refund a bit but not much.  We are filing in MS due to this but you don’t owe any money to them as your income was not enough to incur taxes there.  We continue to itemize in Alabama - that added almost $1k to your refund thanks to the medical expenses.   Everything else looked good. Please let me know if any questions – thanks.</v>
+      </c>
+      <c r="G3" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="H3" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="I3" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="J3" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="K3" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="L3" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="M3" s="2">
         <v>750</v>
       </c>
-      <c r="N2" s="2" t="str">
-        <v>Personal Tax Services - JJ</v>
-      </c>
-      <c r="O2" s="2" t="str">
-        <v>X</v>
-      </c>
-      <c r="P2" s="2" t="str">
-        <v>2022 1040 Return - JJ</v>
-      </c>
-      <c r="Q2" s="2" t="str">
-        <v>none</v>
-      </c>
-      <c r="R2" s="2">
+      <c r="N3" s="2" t="str">
+        <v>Personal Tax Services - JJ</v>
+      </c>
+      <c r="O3" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="P3" s="2" t="str">
+        <v>2023 1040 Return - JJ</v>
+      </c>
+      <c r="Q3" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="R3" s="2">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="str">
+        <v>BC7</v>
+      </c>
+      <c r="C4" s="2" t="str">
+        <v>Brennan, Christopher &amp; Anne</v>
+      </c>
+      <c r="D4" s="2" t="str">
+        <v>Send Out Returns, Bill, and Efile Sigs - InvoiceInTD</v>
+      </c>
+      <c r="E4" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="F4" s="2" t="str">
+        <v>You owe a bit due to a BIG gain on your Vertex share sales (a good thing of course except now when you have to pay taxes on it!).  The gain is taxed at the most favorable long term capital gains rate and we adjusted your cost basis so you weren’t double taxed.  Everything else was very similar to last year.  Hope you are well - let me know if any questions - thanks!</v>
+      </c>
+      <c r="G4" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="H4" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="I4" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="J4" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="K4" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="L4" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="M4" s="2">
+        <v>750</v>
+      </c>
+      <c r="N4" s="2" t="str">
+        <v>Personal Tax Services - JJ</v>
+      </c>
+      <c r="O4" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="P4" s="2" t="str">
+        <v>2023 1040 Return - JJ</v>
+      </c>
+      <c r="Q4" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="R4" s="2">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="str">
+        <v>WM8</v>
+      </c>
+      <c r="C5" s="2" t="str">
+        <v>Walsh, Mary</v>
+      </c>
+      <c r="D5" s="2" t="str">
+        <v>Send Out Returns, Bill, and Efile Sigs - InvoiceInTD</v>
+      </c>
+      <c r="E5" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="F5" s="2" t="str">
+        <v>Your mother had good withholdings and thus the estate is getting a great federal refund.  Additionally there is a nice MA refund as we got $887 for the MA Senior Circuit Breaker Credit.  My condolences again on your loss - let me know if any questions - thanks.</v>
+      </c>
+      <c r="G5" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="H5" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="I5" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="J5" s="2" t="str">
+        <v>MA-Single-TS</v>
+      </c>
+      <c r="K5" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="L5" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="M5" s="2">
+        <v>900</v>
+      </c>
+      <c r="N5" s="2" t="str">
+        <v>Personal Tax Services - JJ</v>
+      </c>
+      <c r="O5" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="P5" s="2" t="str">
+        <v>2023 1040 Return - JJ</v>
+      </c>
+      <c r="Q5" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="R5" s="2">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2">
+        <v>1</v>
+      </c>
+      <c r="B6" s="2" t="str">
+        <v>KS3</v>
+      </c>
+      <c r="C6" s="2" t="str">
+        <v>Kelleher, Stephen</v>
+      </c>
+      <c r="D6" s="2" t="str">
+        <v>Send Out Returns, Bill, and Efile Sigs - InvoiceInTD</v>
+      </c>
+      <c r="E6" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="F6" s="2" t="str">
+        <v>Nice increase in your rental income of $7k and another $7k increase in interest and dividends has you owing a bit as compared to last year but it’s for good reasons!  Again the rental is also the reason why you owe in RI. Glad to see you are still doing the ESPP hopefully that works out for you in the long term.  Hope you are well and as always - please let me know if you have any questions - thanks.</v>
+      </c>
+      <c r="G6" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="H6" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="I6" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="J6" s="2" t="str">
+        <v>MA-Single-TS</v>
+      </c>
+      <c r="K6" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="L6" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="M6" s="2">
+        <v>750</v>
+      </c>
+      <c r="N6" s="2" t="str">
+        <v>Personal Tax Services - JJ</v>
+      </c>
+      <c r="O6" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="P6" s="2" t="str">
+        <v>2023 1040 Return - JJ</v>
+      </c>
+      <c r="Q6" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="R6" s="2">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2">
+        <v>1</v>
+      </c>
+      <c r="B7" s="2" t="str">
+        <v>ST2</v>
+      </c>
+      <c r="C7" s="2" t="str">
+        <v>Sasaki, Tomoaki</v>
+      </c>
+      <c r="D7" s="2" t="str">
+        <v>Send Out Returns, Bill, and Efile Sigs - InvoiceInTD</v>
+      </c>
+      <c r="E7" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="F7" s="2" t="str">
+        <v>You owe a little this year as your wages went up almost $6k and your withholdings went down by $3k from last year.  We noted your backdoor Roth contribution of $6,500 and excluded that in the conversion to a Roth.  Last year we noted your $6k contribution and used it to exclude taxation on the $20k IRA conversion giving you an upfront tax break so that $6k is now taxable this year.  As you are now caught up and only converting $6,500 each year there will be no more catchups or taxable contributions going forward. Let me know if any questions - thanks and hope all is well!</v>
+      </c>
+      <c r="G7" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="H7" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="I7" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="J7" s="2" t="str">
+        <v>MA-Single-TS</v>
+      </c>
+      <c r="K7" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="L7" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="M7" s="2">
+        <v>875</v>
+      </c>
+      <c r="N7" s="2" t="str">
+        <v>Personal Tax Services - JJ</v>
+      </c>
+      <c r="O7" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="P7" s="2" t="str">
+        <v>2023 1040 Return - JJ</v>
+      </c>
+      <c r="Q7" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="R7" s="2">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2">
+        <v>1</v>
+      </c>
+      <c r="B8" s="2" t="str">
+        <v>PR4</v>
+      </c>
+      <c r="C8" s="2" t="str">
+        <v>Pelly, Rachel</v>
+      </c>
+      <c r="D8" s="2" t="str">
+        <v>Send Out Returns, Bill, and Efile Sigs - InvoiceInTD</v>
+      </c>
+      <c r="E8" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="F8" s="2" t="str">
+        <v>BIG refund this year again due to your wages being down a good bit (due to less stock compensation flowing through your W2 for options exercises) and lower capital gains income. Further, you got a $2600 tax credit for energy improvements due to your home renovation.  We of course made sure to deduct your mortgage interest. Everything else looked good. Please let me know if you have any questions – thanks.</v>
+      </c>
+      <c r="G8" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="H8" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="I8" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="J8" s="2" t="str">
+        <v>MA-Single-TS</v>
+      </c>
+      <c r="K8" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="L8" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="M8" s="2">
+        <v>975</v>
+      </c>
+      <c r="N8" s="2" t="str">
+        <v>Personal Tax Services - JJ</v>
+      </c>
+      <c r="O8" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="P8" s="2" t="str">
+        <v>2023 1040 Return - JJ</v>
+      </c>
+      <c r="Q8" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="R8" s="2">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2">
+        <v>1</v>
+      </c>
+      <c r="B9" s="2" t="str">
+        <v>BM11</v>
+      </c>
+      <c r="C9" s="2" t="str">
+        <v>Bildman, Mark</v>
+      </c>
+      <c r="D9" s="2" t="str">
+        <v>Send Out Returns, Bill, and Efile Sigs - InvoiceInTD</v>
+      </c>
+      <c r="E9" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="F9" s="2" t="str">
+        <v>You had some great interest and dividends this year and that is why you owe the slightest of amounts now.  That said it’s good to get interest!  My computer just completely crashed this week but the data was backed up - made me think of how you saved my bacon back in the day!  Hope all is well - let me know if any questions - thanks.</v>
+      </c>
+      <c r="G9" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="H9" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="I9" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="J9" s="2" t="str">
+        <v>MA-Single-TS</v>
+      </c>
+      <c r="K9" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="L9" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="M9" s="2">
+        <v>475</v>
+      </c>
+      <c r="N9" s="2" t="str">
+        <v>Personal Tax Services - JJ</v>
+      </c>
+      <c r="O9" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="P9" s="2" t="str">
+        <v>2023 1040 Return - JJ</v>
+      </c>
+      <c r="Q9" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="R9" s="2">
         <v>2023</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R9"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData/>
+  <dimension ref="A1:R3"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="str">
+        <v>Number</v>
+      </c>
+      <c r="B1" s="2" t="str">
+        <v>ClientID</v>
+      </c>
+      <c r="C1" s="2" t="str">
+        <v>ClientName</v>
+      </c>
+      <c r="D1" s="2" t="str">
+        <v>EmailTemp1</v>
+      </c>
+      <c r="E1" s="2" t="str">
+        <v>EmailTemp2</v>
+      </c>
+      <c r="F1" s="2" t="str">
+        <v>Comment</v>
+      </c>
+      <c r="G1" s="2" t="str">
+        <v>Estimate</v>
+      </c>
+      <c r="H1" s="2" t="str">
+        <v>TaxReturn</v>
+      </c>
+      <c r="I1" s="2" t="str">
+        <v>Signature</v>
+      </c>
+      <c r="J1" s="2" t="str">
+        <v>SignatureTemplate</v>
+      </c>
+      <c r="K1" s="2" t="str">
+        <v>RequireKBA</v>
+      </c>
+      <c r="L1" s="2" t="str">
+        <v>Invoice</v>
+      </c>
+      <c r="M1" s="2" t="str">
+        <v>InvoiceAmount</v>
+      </c>
+      <c r="N1" s="2" t="str">
+        <v>InvoiceTemplate</v>
+      </c>
+      <c r="O1" s="2" t="str">
+        <v>Closer</v>
+      </c>
+      <c r="P1" s="2" t="str">
+        <v>Pipeline</v>
+      </c>
+      <c r="Q1" s="2" t="str">
+        <v>Seal</v>
+      </c>
+      <c r="R1" s="2" t="str">
+        <v>YearToSeal</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="str">
+        <v>SF2</v>
+      </c>
+      <c r="C2" s="2" t="str">
+        <v>Finney, Stephen</v>
+      </c>
+      <c r="D2" s="2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E2" s="2" t="str">
+        <v>N</v>
+      </c>
+      <c r="F2" s="2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G2" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="H2" s="2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I2" s="2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="J2" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="K2" s="2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="L2" s="2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M2" s="2">
+        <v>875</v>
+      </c>
+      <c r="N2" s="2" t="str">
+        <v>Personal Tax Services - JJ</v>
+      </c>
+      <c r="O2" s="2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="P2" s="2" t="str">
+        <v>2023 1040 Return - JJ</v>
+      </c>
+      <c r="Q2" s="2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="R2" s="2">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="str">
+        <v>AA1</v>
+      </c>
+      <c r="C3" s="2" t="str">
+        <v>Aiken, Kathleen &amp; Carillo, Catherine</v>
+      </c>
+      <c r="D3" s="2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E3" s="2" t="str">
+        <v>N</v>
+      </c>
+      <c r="F3" s="2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G3" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="H3" s="2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I3" s="2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="J3" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="K3" s="2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="L3" s="2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M3" s="2">
+        <v>750</v>
+      </c>
+      <c r="N3" s="2" t="str">
+        <v>Personal Tax Services - JJ</v>
+      </c>
+      <c r="O3" s="2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="P3" s="2" t="str">
+        <v>2023 1040 Return - JJ</v>
+      </c>
+      <c r="Q3" s="2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="R3" s="2">
+        <v>2023</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/AutomateSendingOutTaxReturnsV3.xlsx
+++ b/AutomateSendingOutTaxReturnsV3.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2FC91C0-6F9C-4FA8-BF6C-505B14C2083A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C231160-67DF-4C7E-A2D3-34D6C5C95844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ClientList" sheetId="1" r:id="rId1"/>
@@ -13,12 +13,25 @@
     <sheet name="Log" sheetId="3" r:id="rId3"/>
     <sheet name="SuccessLog" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="69">
   <si>
     <t>Number</t>
   </si>
@@ -74,30 +87,69 @@
     <t>YearToSeal</t>
   </si>
   <si>
+    <t>BJ12</t>
+  </si>
+  <si>
+    <t>Barrera, Julie</t>
+  </si>
+  <si>
+    <t>Send Out Returns, Bill, and Efile Sigs - InvoiceInTD</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>MA-Single-TS</t>
+  </si>
+  <si>
+    <t>Personal Tax Services - JJ</t>
+  </si>
+  <si>
+    <t>2023 1040 Return - JJ</t>
+  </si>
+  <si>
+    <t>LC7</t>
+  </si>
+  <si>
+    <t>Lesher, Christian &amp; Sara</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>SF2</t>
+  </si>
+  <si>
+    <t>Finney, Stephen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Big increase in income this year compared to last! Your wages almost doubled and your withholdings kept up for the most part. You owe a little but not too much considering your overall income. We noted your $6.5k backdoor Roth IRA contribution and made sure to make it non-taxable. Finally, we also made sure to file you in 2 states - MA and RI. Everything else looked good. Please let me know if any questions – thanks. </t>
+  </si>
+  <si>
+    <t>AA1</t>
+  </si>
+  <si>
+    <t>Aiken, Kathleen &amp; Carillo, Catherine</t>
+  </si>
+  <si>
+    <t>Very similar to last year income wise in nearly all respects EXCEPT for your gambling winnings  – nice! It lowered your refund a bit but not much.  We are filing in MS due to this but you don’t owe any money to them as your income was not enough to incur taxes there.  We continue to itemize in Alabama - that added almost $1k to your refund thanks to the medical expenses.   Everything else looked good. Please let me know if any questions – thanks.</t>
+  </si>
+  <si>
     <t>BC7</t>
   </si>
   <si>
     <t>Brennan, Christopher &amp; Anne</t>
   </si>
   <si>
-    <t>Send Out Returns, Bill, and Efile Sigs - InvoiceInTD</t>
-  </si>
-  <si>
-    <t>none</t>
-  </si>
-  <si>
     <t>You owe a bit due to a BIG gain on your Vertex share sales (a good thing of course except now when you have to pay taxes on it!).  The gain is taxed at the most favorable long term capital gains rate and we adjusted your cost basis so you weren’t double taxed.  Everything else was very similar to last year.  Hope you are well - let me know if any questions - thanks!</t>
   </si>
   <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>Personal Tax Services - JJ</t>
-  </si>
-  <si>
-    <t>2023 1040 Return - JJ</t>
-  </si>
-  <si>
     <t>WM8</t>
   </si>
   <si>
@@ -107,9 +159,6 @@
     <t>Your mother had good withholdings and thus the estate is getting a great federal refund.  Additionally there is a nice MA refund as we got $887 for the MA Senior Circuit Breaker Credit.  My condolences again on your loss - let me know if any questions - thanks.</t>
   </si>
   <si>
-    <t>MA-Single-TS</t>
-  </si>
-  <si>
     <t>KS3</t>
   </si>
   <si>
@@ -146,47 +195,67 @@
     <t>You had some great interest and dividends this year and that is why you owe the slightest of amounts now.  That said it’s good to get interest!  My computer just completely crashed this week but the data was backed up - made me think of how you saved my bacon back in the day!  Hope all is well - let me know if any questions - thanks.</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>SF2</t>
-  </si>
-  <si>
-    <t>Finney, Stephen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Big increase in income this year compared to last! Your wages almost doubled and your withholdings kept up for the most part. You owe a little but not too much considering your overall income. We noted your $6.5k backdoor Roth IRA contribution and made sure to make it non-taxable. Finally, we also made sure to file you in 2 states - MA and RI. Everything else looked good. Please let me know if any questions – thanks. </t>
-  </si>
-  <si>
-    <t>AA1</t>
-  </si>
-  <si>
-    <t>Aiken, Kathleen &amp; Carillo, Catherine</t>
-  </si>
-  <si>
-    <t>Very similar to last year income wise in nearly all respects EXCEPT for your gambling winnings  – nice! It lowered your refund a bit but not much.  We are filing in MS due to this but you don’t owe any money to them as your income was not enough to incur taxes there.  We continue to itemize in Alabama - that added almost $1k to your refund thanks to the medical expenses.   Everything else looked good. Please let me know if any questions – thanks.</t>
-  </si>
-  <si>
-    <t>SD3</t>
-  </si>
-  <si>
-    <t>Single, Dummy</t>
+    <t>BJ13</t>
+  </si>
+  <si>
+    <t>Bonanno, Jasmine</t>
+  </si>
+  <si>
+    <t>Second verse, almost the same as the first! Very similar to last year wage income wise – you owe a little but not too much considering your overall income. Your wages went up $17k and your withholdings kept up. You didn't have a lot of capital gains ($4k) - they were all long term and we made sure to adjust the cost basis to ensure you weren’t double taxed. Finally we told you about the Roth income limit so that you took out $1,090 from it so you wouldn’t be penalized. You should be aware of this limit going forward and use the backdoor Roth method to get money into a Roth going forward. Everything else looked good. Please let me know if any questions – thanks.</t>
+  </si>
+  <si>
+    <t>CK6</t>
+  </si>
+  <si>
+    <t>Carmody, Karen</t>
+  </si>
+  <si>
+    <t>Your business swung from a loss to a nice income of $21k after taking out all possible deductions. Your new job had some nice withholdings and thus you don’t owe that much even though you had sizable business income. Everything else stayed similar to previous years. Please let me know if any questions - thanks.</t>
+  </si>
+  <si>
+    <t>GA14</t>
+  </si>
+  <si>
+    <t>Ganguly, Auroop &amp; Debashree</t>
+  </si>
+  <si>
+    <t>Similar to last year wage income wise – you owe a little but not too much considering your overall income. Your wages went up $75k and your withholdings kept up for the most part. We reported Auroop’s side income properly, including creating a Schedule E for the royalties. The new thing was Shree’s business - we added that and took all available deductions. This reduced the amount you owed in taxes by $972. Everything else looked good. Please let me know if any questions – thanks.</t>
+  </si>
+  <si>
+    <t>WA6</t>
+  </si>
+  <si>
+    <t>Walter, Johannes &amp; Sever, Sanja</t>
+  </si>
+  <si>
+    <t>Nice refund this year as you got most of your withholdings back due to slightly less income - everything was the same generally speaking as last year but just a little less business income. We took all possible tax deductions on each of your business returns, including the home office deduction. I set you up with a new Schedule E to report Sanja’s royalty income. Finally, made sure to discuss with you the tax implications of Sanja moving to Texas. All in all, a great year for you with exciting changes coming up! Let me know if any questions - thanks!</t>
+  </si>
+  <si>
+    <t>GB3</t>
+  </si>
+  <si>
+    <t>Garcia Barrantes, Pedro &amp; Betancourt, Rosanna</t>
+  </si>
+  <si>
+    <t>Fixed the Schedule B for Costa Rica - thanks!</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -210,21 +279,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -232,18 +297,40 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -583,10 +670,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -642,78 +729,300 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" t="s">
+    <row r="2" spans="1:18" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="5">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="E2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="H2" t="s">
+      <c r="K2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" s="5">
+        <v>875</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="R2" s="5">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="5">
+        <v>1</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2">
-        <v>750</v>
-      </c>
-      <c r="N2" t="s">
+      <c r="K3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="5">
+        <v>650</v>
+      </c>
+      <c r="N3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="O2" t="s">
-        <v>23</v>
-      </c>
-      <c r="P2" t="s">
+      <c r="O3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P3" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="Q2" t="s">
-        <v>23</v>
-      </c>
-      <c r="R2">
+      <c r="Q3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="R3" s="5">
         <v>2023</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="4" spans="1:18" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="1:18" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="6" spans="1:18" ht="15.5" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="1:18" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="5">
+        <v>1</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M4" s="5">
+        <v>975</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="O4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="5">
+        <v>1</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M5" s="5">
+        <v>950</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="O5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P5" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="76.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="5">
+        <v>1</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="O6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P6" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="R6" s="5">
+        <v>2023</v>
+      </c>
+    </row>
     <row r="7" spans="1:18" ht="15.5" x14ac:dyDescent="0.35"/>
+    <row r="8" spans="1:18" ht="15.5" x14ac:dyDescent="0.35"/>
+    <row r="9" spans="1:18" ht="15.5" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:R1 A2 D2:R2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:R1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
@@ -783,46 +1092,46 @@
         <v>19</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="J2" t="s">
-        <v>21</v>
-      </c>
       <c r="K2" s="3" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="M2">
-        <v>750</v>
+        <v>875</v>
       </c>
       <c r="N2" t="s">
         <v>24</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="P2" t="s">
         <v>25</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="R2">
         <v>2023</v>
@@ -839,279 +1148,56 @@
         <v>27</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>43</v>
+        <v>28</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>23</v>
+        <v>28</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="J3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="M3">
-        <v>900</v>
+        <v>750</v>
       </c>
       <c r="N3" t="s">
         <v>24</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="P3" t="s">
         <v>25</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="R3">
         <v>2023</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="J4" t="s">
-        <v>29</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M4">
-        <v>750</v>
-      </c>
-      <c r="N4" t="s">
-        <v>24</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="P4" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="R4">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>1</v>
-      </c>
-      <c r="B5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="J5" t="s">
-        <v>29</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M5">
-        <v>875</v>
-      </c>
-      <c r="N5" t="s">
-        <v>24</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="P5" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="R5">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6">
-        <v>1</v>
-      </c>
-      <c r="B6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="J6" t="s">
-        <v>29</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M6">
-        <v>975</v>
-      </c>
-      <c r="N6" t="s">
-        <v>24</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="P6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="R6">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7">
-        <v>1</v>
-      </c>
-      <c r="B7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="J7" t="s">
-        <v>29</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M7">
-        <v>475</v>
-      </c>
-      <c r="N7" t="s">
-        <v>24</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="P7" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q7" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="R7">
-        <v>2023</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:R7" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:R3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1182,10 +1268,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
         <v>20</v>
@@ -1194,25 +1280,25 @@
         <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="G2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J2" t="s">
         <v>21</v>
       </c>
       <c r="K2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M2">
         <v>875</v>
@@ -1221,13 +1307,13 @@
         <v>24</v>
       </c>
       <c r="O2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P2" t="s">
         <v>25</v>
       </c>
       <c r="Q2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R2">
         <v>2023</v>
@@ -1238,10 +1324,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
         <v>20</v>
@@ -1250,25 +1336,25 @@
         <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="G3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J3" t="s">
         <v>21</v>
       </c>
       <c r="K3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M3">
         <v>750</v>
@@ -1277,13 +1363,13 @@
         <v>24</v>
       </c>
       <c r="O3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P3" t="s">
         <v>25</v>
       </c>
       <c r="Q3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R3">
         <v>2023</v>
@@ -1294,10 +1380,10 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
         <v>20</v>
@@ -1306,25 +1392,25 @@
         <v>21</v>
       </c>
       <c r="F4" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="G4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J4" t="s">
         <v>21</v>
       </c>
       <c r="K4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M4">
         <v>750</v>
@@ -1333,13 +1419,13 @@
         <v>24</v>
       </c>
       <c r="O4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P4" t="s">
         <v>25</v>
       </c>
       <c r="Q4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R4">
         <v>2023</v>
@@ -1350,10 +1436,10 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
         <v>20</v>
@@ -1362,25 +1448,25 @@
         <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="G5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" t="s">
         <v>23</v>
       </c>
-      <c r="H5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" t="s">
-        <v>23</v>
-      </c>
-      <c r="J5" t="s">
-        <v>29</v>
-      </c>
       <c r="K5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M5">
         <v>900</v>
@@ -1389,13 +1475,13 @@
         <v>24</v>
       </c>
       <c r="O5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P5" t="s">
         <v>25</v>
       </c>
       <c r="Q5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R5">
         <v>2023</v>
@@ -1406,10 +1492,10 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
         <v>20</v>
@@ -1418,25 +1504,25 @@
         <v>21</v>
       </c>
       <c r="F6" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="G6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" t="s">
         <v>23</v>
       </c>
-      <c r="H6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J6" t="s">
-        <v>29</v>
-      </c>
       <c r="K6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M6">
         <v>750</v>
@@ -1445,13 +1531,13 @@
         <v>24</v>
       </c>
       <c r="O6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P6" t="s">
         <v>25</v>
       </c>
       <c r="Q6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R6">
         <v>2023</v>
@@ -1462,10 +1548,10 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
         <v>20</v>
@@ -1474,25 +1560,25 @@
         <v>21</v>
       </c>
       <c r="F7" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="G7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" t="s">
         <v>23</v>
       </c>
-      <c r="H7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J7" t="s">
-        <v>29</v>
-      </c>
       <c r="K7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M7">
         <v>875</v>
@@ -1501,13 +1587,13 @@
         <v>24</v>
       </c>
       <c r="O7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P7" t="s">
         <v>25</v>
       </c>
       <c r="Q7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R7">
         <v>2023</v>
@@ -1518,10 +1604,10 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
         <v>20</v>
@@ -1530,25 +1616,25 @@
         <v>21</v>
       </c>
       <c r="F8" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" t="s">
         <v>23</v>
       </c>
-      <c r="H8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I8" t="s">
-        <v>23</v>
-      </c>
-      <c r="J8" t="s">
-        <v>29</v>
-      </c>
       <c r="K8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M8">
         <v>975</v>
@@ -1557,13 +1643,13 @@
         <v>24</v>
       </c>
       <c r="O8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P8" t="s">
         <v>25</v>
       </c>
       <c r="Q8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R8">
         <v>2023</v>
@@ -1574,10 +1660,10 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D9" t="s">
         <v>20</v>
@@ -1586,25 +1672,25 @@
         <v>21</v>
       </c>
       <c r="F9" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="G9" t="s">
+        <v>22</v>
+      </c>
+      <c r="H9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" t="s">
         <v>23</v>
       </c>
-      <c r="H9" t="s">
-        <v>23</v>
-      </c>
-      <c r="I9" t="s">
-        <v>23</v>
-      </c>
-      <c r="J9" t="s">
-        <v>29</v>
-      </c>
       <c r="K9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M9">
         <v>475</v>
@@ -1613,13 +1699,13 @@
         <v>24</v>
       </c>
       <c r="O9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P9" t="s">
         <v>25</v>
       </c>
       <c r="Q9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R9">
         <v>2023</v>
@@ -1699,37 +1785,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="G2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H2" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="I2" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="J2" t="s">
         <v>21</v>
       </c>
       <c r="K2" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="L2" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="M2">
         <v>875</v>
@@ -1738,13 +1824,13 @@
         <v>24</v>
       </c>
       <c r="O2" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="P2" t="s">
         <v>25</v>
       </c>
       <c r="Q2" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="R2">
         <v>2023</v>
@@ -1755,37 +1841,37 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="F3" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="G3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H3" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="I3" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="J3" t="s">
         <v>21</v>
       </c>
       <c r="K3" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="L3" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="M3">
         <v>750</v>
@@ -1794,13 +1880,13 @@
         <v>24</v>
       </c>
       <c r="O3" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="P3" t="s">
         <v>25</v>
       </c>
       <c r="Q3" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="R3">
         <v>2023</v>

--- a/AutomateSendingOutTaxReturnsV3.xlsx
+++ b/AutomateSendingOutTaxReturnsV3.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C231160-67DF-4C7E-A2D3-34D6C5C95844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD7FB0C7-7137-43DB-AF2D-A8F874BC2105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ClientList" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="57">
   <si>
     <t>Number</t>
   </si>
@@ -195,67 +195,26 @@
     <t>You had some great interest and dividends this year and that is why you owe the slightest of amounts now.  That said it’s good to get interest!  My computer just completely crashed this week but the data was backed up - made me think of how you saved my bacon back in the day!  Hope all is well - let me know if any questions - thanks.</t>
   </si>
   <si>
-    <t>BJ13</t>
-  </si>
-  <si>
-    <t>Bonanno, Jasmine</t>
-  </si>
-  <si>
-    <t>Second verse, almost the same as the first! Very similar to last year wage income wise – you owe a little but not too much considering your overall income. Your wages went up $17k and your withholdings kept up. You didn't have a lot of capital gains ($4k) - they were all long term and we made sure to adjust the cost basis to ensure you weren’t double taxed. Finally we told you about the Roth income limit so that you took out $1,090 from it so you wouldn’t be penalized. You should be aware of this limit going forward and use the backdoor Roth method to get money into a Roth going forward. Everything else looked good. Please let me know if any questions – thanks.</t>
-  </si>
-  <si>
-    <t>CK6</t>
-  </si>
-  <si>
-    <t>Carmody, Karen</t>
-  </si>
-  <si>
-    <t>Your business swung from a loss to a nice income of $21k after taking out all possible deductions. Your new job had some nice withholdings and thus you don’t owe that much even though you had sizable business income. Everything else stayed similar to previous years. Please let me know if any questions - thanks.</t>
-  </si>
-  <si>
-    <t>GA14</t>
-  </si>
-  <si>
-    <t>Ganguly, Auroop &amp; Debashree</t>
-  </si>
-  <si>
-    <t>Similar to last year wage income wise – you owe a little but not too much considering your overall income. Your wages went up $75k and your withholdings kept up for the most part. We reported Auroop’s side income properly, including creating a Schedule E for the royalties. The new thing was Shree’s business - we added that and took all available deductions. This reduced the amount you owed in taxes by $972. Everything else looked good. Please let me know if any questions – thanks.</t>
-  </si>
-  <si>
-    <t>WA6</t>
-  </si>
-  <si>
-    <t>Walter, Johannes &amp; Sever, Sanja</t>
-  </si>
-  <si>
-    <t>Nice refund this year as you got most of your withholdings back due to slightly less income - everything was the same generally speaking as last year but just a little less business income. We took all possible tax deductions on each of your business returns, including the home office deduction. I set you up with a new Schedule E to report Sanja’s royalty income. Finally, made sure to discuss with you the tax implications of Sanja moving to Texas. All in all, a great year for you with exciting changes coming up! Let me know if any questions - thanks!</t>
-  </si>
-  <si>
-    <t>GB3</t>
-  </si>
-  <si>
-    <t>Garcia Barrantes, Pedro &amp; Betancourt, Rosanna</t>
-  </si>
-  <si>
-    <t>Fixed the Schedule B for Costa Rica - thanks!</t>
+    <t>SD3</t>
+  </si>
+  <si>
+    <t>Single, Dummy</t>
+  </si>
+  <si>
+    <t>MA-Single</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <name val="Calibri"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -282,14 +241,8 @@
         <fgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -297,40 +250,16 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -670,13 +599,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:R2"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="14" max="14" width="14.58203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
         <v>1</v>
       </c>
@@ -729,293 +658,66 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="5">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" t="s">
         <v>56</v>
       </c>
-      <c r="G2" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M2" s="5">
-        <v>875</v>
-      </c>
-      <c r="N2" s="6" t="s">
+      <c r="K2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2">
+        <v>10</v>
+      </c>
+      <c r="N2" t="s">
         <v>24</v>
       </c>
-      <c r="O2" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P2" s="6" t="s">
+      <c r="O2" t="s">
+        <v>22</v>
+      </c>
+      <c r="P2" t="s">
         <v>25</v>
       </c>
-      <c r="Q2" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="R2" s="5">
+      <c r="Q2" t="s">
+        <v>22</v>
+      </c>
+      <c r="R2">
         <v>2023</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="5">
-        <v>1</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M3" s="5">
-        <v>650</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P3" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q3" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="R3" s="5">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="5">
-        <v>1</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M4" s="5">
-        <v>975</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="O4" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P4" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q4" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="R4" s="5">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="5">
-        <v>1</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L5" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M5" s="5">
-        <v>950</v>
-      </c>
-      <c r="N5" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="O5" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P5" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q5" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="R5" s="5">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" ht="76.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="5">
-        <v>1</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M6" s="5">
-        <v>0</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="O6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P6" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q6" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="R6" s="5">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="8" spans="1:18" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="9" spans="1:18" ht="15.5" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:R1" numberStoredAsText="1"/>
+    <ignoredError sqref="B1:R1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1023,9 +725,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1081,7 +783,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1137,7 +839,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1205,9 +907,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:R9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1263,7 +965,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1319,7 +1021,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1375,7 +1077,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1431,7 +1133,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1</v>
       </c>
@@ -1487,7 +1189,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>1</v>
       </c>
@@ -1543,7 +1245,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1</v>
       </c>
@@ -1599,7 +1301,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>1</v>
       </c>
@@ -1655,7 +1357,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1</v>
       </c>
@@ -1722,9 +1424,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:R3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1780,7 +1482,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1836,7 +1538,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>

--- a/AutomateSendingOutTaxReturnsV3.xlsx
+++ b/AutomateSendingOutTaxReturnsV3.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B767EBED-C302-48FE-9829-1C1F63DD519F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5440718-5D6C-4C98-8B70-8159329D5546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ClientList" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="18">
   <si>
     <t>Number</t>
   </si>
@@ -85,30 +85,6 @@
   </si>
   <si>
     <t>YearToSeal</t>
-  </si>
-  <si>
-    <t>Send Out Returns, Bill, and Efile Sigs - InvoiceInTD</t>
-  </si>
-  <si>
-    <t>none</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>Personal Tax Services - JJ</t>
-  </si>
-  <si>
-    <t>2023 1040 Return - JJ</t>
-  </si>
-  <si>
-    <t>SD3</t>
-  </si>
-  <si>
-    <t>Single, Dummy</t>
-  </si>
-  <si>
-    <t>MA-Single</t>
   </si>
 </sst>
 </file>
@@ -482,13 +458,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R2"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="14" max="14" width="14.58203125" bestFit="1" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:R1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
@@ -539,68 +515,12 @@
       </c>
       <c r="R1" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2">
-        <v>10</v>
-      </c>
-      <c r="N2" t="s">
-        <v>21</v>
-      </c>
-      <c r="O2" t="s">
-        <v>20</v>
-      </c>
-      <c r="P2" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>20</v>
-      </c>
-      <c r="R2">
-        <v>2023</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="B1:R1" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:R1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -608,9 +528,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R1"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -678,9 +598,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:R1"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -747,9 +667,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:R1"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>

--- a/AutomateSendingOutTaxReturnsV3.xlsx
+++ b/AutomateSendingOutTaxReturnsV3.xlsx
@@ -1,97 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
-  <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5440718-5D6C-4C98-8B70-8159329D5546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook" filterPrivacy="true"/>
   <sheets>
     <sheet name="ClientList" sheetId="1" r:id="rId1"/>
     <sheet name="ClientSummary" sheetId="2" r:id="rId2"/>
     <sheet name="Log" sheetId="3" r:id="rId3"/>
     <sheet name="SuccessLog" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="18">
-  <si>
-    <t>Number</t>
-  </si>
-  <si>
-    <t>ClientID</t>
-  </si>
-  <si>
-    <t>ClientName</t>
-  </si>
-  <si>
-    <t>EmailTemp1</t>
-  </si>
-  <si>
-    <t>EmailTemp2</t>
-  </si>
-  <si>
-    <t>Comment</t>
-  </si>
-  <si>
-    <t>Estimate</t>
-  </si>
-  <si>
-    <t>TaxReturn</t>
-  </si>
-  <si>
-    <t>Signature</t>
-  </si>
-  <si>
-    <t>SignatureTemplate</t>
-  </si>
-  <si>
-    <t>RequireKBA</t>
-  </si>
-  <si>
-    <t>Invoice</t>
-  </si>
-  <si>
-    <t>InvoiceAmount</t>
-  </si>
-  <si>
-    <t>InvoiceTemplate</t>
-  </si>
-  <si>
-    <t>Closer</t>
-  </si>
-  <si>
-    <t>Pipeline</t>
-  </si>
-  <si>
-    <t>Seal</t>
-  </si>
-  <si>
-    <t>YearToSeal</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+    </font>
     <font>
       <sz val="12"/>
       <name val="Calibri"/>
@@ -99,13 +26,24 @@
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill patternType="none">
+        <bgColor/>
+      </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="gray125">
+        <bgColor/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -114,25 +52,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -457,278 +389,271 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:R2"/>
   <sheetData>
-    <row r="1" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1">
+      <c r="A1" s="2" t="str">
+        <v>Number</v>
+      </c>
+      <c r="B1" s="2" t="str">
+        <v>ClientID</v>
+      </c>
+      <c r="C1" s="2" t="str">
+        <v>ClientName</v>
+      </c>
+      <c r="D1" s="2" t="str">
+        <v>EmailTemp1</v>
+      </c>
+      <c r="E1" s="2" t="str">
+        <v>EmailTemp2</v>
+      </c>
+      <c r="F1" s="2" t="str">
+        <v>Comment</v>
+      </c>
+      <c r="G1" s="2" t="str">
+        <v>Estimate</v>
+      </c>
+      <c r="H1" s="2" t="str">
+        <v>TaxReturn</v>
+      </c>
+      <c r="I1" s="2" t="str">
+        <v>Signature</v>
+      </c>
+      <c r="J1" s="2" t="str">
+        <v>SignatureTemplate</v>
+      </c>
+      <c r="K1" s="2" t="str">
+        <v>RequireKBA</v>
+      </c>
+      <c r="L1" s="2" t="str">
+        <v>Invoice</v>
+      </c>
+      <c r="M1" s="2" t="str">
+        <v>InvoiceAmount</v>
+      </c>
+      <c r="N1" s="2" t="str">
+        <v>InvoiceTemplate</v>
+      </c>
+      <c r="O1" s="2" t="str">
+        <v>Closer</v>
+      </c>
+      <c r="P1" s="2" t="str">
+        <v>Pipeline</v>
+      </c>
+      <c r="Q1" s="2" t="str">
+        <v>Seal</v>
+      </c>
+      <c r="R1" s="2" t="str">
+        <v>YearToSeal</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
+      <c r="B2" s="2" t="str">
+        <v>SD3</v>
+      </c>
+      <c r="C2" s="2" t="str">
+        <v>Single, Dummy</v>
+      </c>
+      <c r="D2" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="E2" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="F2" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="G2" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="H2" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="I2" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="J2" s="2" t="str">
+        <v>MA-Single</v>
+      </c>
+      <c r="K2" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="L2" s="2" t="str">
+        <v>X</v>
+      </c>
+      <c r="M2" s="2">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" t="s">
-        <v>17</v>
+      <c r="N2" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="O2" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="P2" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="Q2" s="2" t="str">
+        <v>none</v>
+      </c>
+      <c r="R2" s="2" t="str">
+        <v>none</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:R1" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1"/>
+  <sheetData/>
   <ignoredErrors>
-    <ignoredError sqref="A1:R1" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:R1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" t="s">
-        <v>17</v>
+    <row r="1">
+      <c r="A1" s="2" t="str">
+        <v>Number</v>
+      </c>
+      <c r="B1" s="2" t="str">
+        <v>ClientID</v>
+      </c>
+      <c r="C1" s="2" t="str">
+        <v>ClientName</v>
+      </c>
+      <c r="D1" s="2" t="str">
+        <v>EmailTemp1</v>
+      </c>
+      <c r="E1" s="2" t="str">
+        <v>EmailTemp2</v>
+      </c>
+      <c r="F1" s="2" t="str">
+        <v>Comment</v>
+      </c>
+      <c r="G1" s="2" t="str">
+        <v>Estimate</v>
+      </c>
+      <c r="H1" s="2" t="str">
+        <v>TaxReturn</v>
+      </c>
+      <c r="I1" s="2" t="str">
+        <v>Signature</v>
+      </c>
+      <c r="J1" s="2" t="str">
+        <v>SignatureTemplate</v>
+      </c>
+      <c r="K1" s="2" t="str">
+        <v>RequireKBA</v>
+      </c>
+      <c r="L1" s="2" t="str">
+        <v>Invoice</v>
+      </c>
+      <c r="M1" s="2" t="str">
+        <v>InvoiceAmount</v>
+      </c>
+      <c r="N1" s="2" t="str">
+        <v>InvoiceTemplate</v>
+      </c>
+      <c r="O1" s="2" t="str">
+        <v>Closer</v>
+      </c>
+      <c r="P1" s="2" t="str">
+        <v>Pipeline</v>
+      </c>
+      <c r="Q1" s="2" t="str">
+        <v>Seal</v>
+      </c>
+      <c r="R1" s="2" t="str">
+        <v>YearToSeal</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:R1" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:R1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" t="s">
-        <v>17</v>
+    <row r="1">
+      <c r="A1" s="2" t="str">
+        <v>Number</v>
+      </c>
+      <c r="B1" s="2" t="str">
+        <v>ClientID</v>
+      </c>
+      <c r="C1" s="2" t="str">
+        <v>ClientName</v>
+      </c>
+      <c r="D1" s="2" t="str">
+        <v>EmailTemp1</v>
+      </c>
+      <c r="E1" s="2" t="str">
+        <v>EmailTemp2</v>
+      </c>
+      <c r="F1" s="2" t="str">
+        <v>Comment</v>
+      </c>
+      <c r="G1" s="2" t="str">
+        <v>Estimate</v>
+      </c>
+      <c r="H1" s="2" t="str">
+        <v>TaxReturn</v>
+      </c>
+      <c r="I1" s="2" t="str">
+        <v>Signature</v>
+      </c>
+      <c r="J1" s="2" t="str">
+        <v>SignatureTemplate</v>
+      </c>
+      <c r="K1" s="2" t="str">
+        <v>RequireKBA</v>
+      </c>
+      <c r="L1" s="2" t="str">
+        <v>Invoice</v>
+      </c>
+      <c r="M1" s="2" t="str">
+        <v>InvoiceAmount</v>
+      </c>
+      <c r="N1" s="2" t="str">
+        <v>InvoiceTemplate</v>
+      </c>
+      <c r="O1" s="2" t="str">
+        <v>Closer</v>
+      </c>
+      <c r="P1" s="2" t="str">
+        <v>Pipeline</v>
+      </c>
+      <c r="Q1" s="2" t="str">
+        <v>Seal</v>
+      </c>
+      <c r="R1" s="2" t="str">
+        <v>YearToSeal</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:R1" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R1"/>
   </ignoredErrors>
 </worksheet>
 </file>